--- a/research/traditional_assets/database/data/argentina/argentina_homebuilding.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_homebuilding.xlsx
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.882</v>
+        <v>0.488</v>
       </c>
       <c r="G2">
-        <v>-0.0961006289308176</v>
+        <v>-0.05170529801324504</v>
       </c>
       <c r="H2">
-        <v>-0.09622641509433962</v>
+        <v>-0.05198675496688742</v>
       </c>
       <c r="I2">
-        <v>-0.1134171907756813</v>
+        <v>-0.1445364238410596</v>
       </c>
       <c r="J2">
-        <v>-0.1134171907756813</v>
+        <v>-0.1445364238410596</v>
       </c>
       <c r="K2">
-        <v>-42.1</v>
+        <v>-16.2</v>
       </c>
       <c r="L2">
-        <v>-0.8825995807127882</v>
+        <v>-0.2682119205298013</v>
       </c>
       <c r="M2">
-        <v>30.1</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8985074626865672</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.7149643705463183</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +627,76 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>30.1</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>2.42</v>
+        <v>4.95</v>
       </c>
       <c r="V2">
-        <v>0.07223880597014926</v>
+        <v>0.1749116607773852</v>
       </c>
       <c r="W2">
-        <v>-0.5096852300242132</v>
+        <v>-0.36</v>
       </c>
       <c r="X2">
-        <v>0.4973749460447112</v>
+        <v>0.4878139353778094</v>
       </c>
       <c r="Y2">
-        <v>-1.007060176068924</v>
+        <v>-0.8478139353778094</v>
       </c>
       <c r="Z2">
-        <v>0.3964428191489363</v>
+        <v>0.7973597359735973</v>
       </c>
       <c r="AA2">
-        <v>-0.04496343085106384</v>
+        <v>-0.1152475247524753</v>
       </c>
       <c r="AB2">
-        <v>0.2497513852772124</v>
+        <v>0.300241699047213</v>
       </c>
       <c r="AC2">
-        <v>-0.2947148161282762</v>
+        <v>-0.4154892237996882</v>
       </c>
       <c r="AD2">
-        <v>54.5</v>
+        <v>31.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>54.5</v>
+        <v>31.4</v>
       </c>
       <c r="AG2">
-        <v>52.08</v>
+        <v>26.45</v>
       </c>
       <c r="AH2">
-        <v>0.6193181818181818</v>
+        <v>0.5259631490787269</v>
       </c>
       <c r="AI2">
-        <v>0.5521783181357649</v>
+        <v>0.4937106918238993</v>
       </c>
       <c r="AJ2">
-        <v>0.6085534003271792</v>
+        <v>0.4831050228310502</v>
       </c>
       <c r="AK2">
-        <v>0.5409223099293726</v>
+        <v>0.4509803921568627</v>
       </c>
       <c r="AL2">
-        <v>9.32</v>
+        <v>7.95</v>
       </c>
       <c r="AM2">
-        <v>8.140000000000001</v>
+        <v>6.11</v>
       </c>
       <c r="AN2">
-        <v>-10.30245746691871</v>
+        <v>-3.64692218350755</v>
       </c>
       <c r="AO2">
-        <v>-0.5804721030042919</v>
+        <v>-1.09811320754717</v>
       </c>
       <c r="AP2">
-        <v>-9.844990548204159</v>
+        <v>-3.072009291521487</v>
       </c>
       <c r="AQ2">
-        <v>-0.6646191646191646</v>
+        <v>-1.428805237315875</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TGLT S.A. (BASE:TGLT)</t>
+          <t>GCDI S.A. (BASE:GCDI)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,34 +716,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.882</v>
+        <v>0.488</v>
       </c>
       <c r="G3">
-        <v>-0.0961006289308176</v>
+        <v>-0.05170529801324504</v>
       </c>
       <c r="H3">
-        <v>-0.09622641509433962</v>
+        <v>-0.05198675496688742</v>
       </c>
       <c r="I3">
-        <v>-0.1134171907756813</v>
+        <v>-0.1445364238410596</v>
       </c>
       <c r="J3">
-        <v>-0.1134171907756813</v>
+        <v>-0.1445364238410596</v>
       </c>
       <c r="K3">
-        <v>-42.1</v>
+        <v>-16.2</v>
       </c>
       <c r="L3">
-        <v>-0.8825995807127882</v>
+        <v>-0.2682119205298013</v>
       </c>
       <c r="M3">
-        <v>30.1</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.8985074626865672</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.7149643705463183</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,79 +755,76 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>30.1</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>2.42</v>
+        <v>4.95</v>
       </c>
       <c r="V3">
-        <v>0.07223880597014926</v>
+        <v>0.1749116607773852</v>
       </c>
       <c r="W3">
-        <v>-0.5096852300242132</v>
+        <v>-0.36</v>
       </c>
       <c r="X3">
-        <v>0.4973749460447112</v>
+        <v>0.4878139353778094</v>
       </c>
       <c r="Y3">
-        <v>-1.007060176068924</v>
+        <v>-0.8478139353778094</v>
       </c>
       <c r="Z3">
-        <v>0.3964428191489363</v>
+        <v>0.7973597359735973</v>
       </c>
       <c r="AA3">
-        <v>-0.04496343085106384</v>
+        <v>-0.1152475247524753</v>
       </c>
       <c r="AB3">
-        <v>0.2497513852772124</v>
+        <v>0.300241699047213</v>
       </c>
       <c r="AC3">
-        <v>-0.2947148161282762</v>
+        <v>-0.4154892237996882</v>
       </c>
       <c r="AD3">
-        <v>54.5</v>
+        <v>31.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>54.5</v>
+        <v>31.4</v>
       </c>
       <c r="AG3">
-        <v>52.08</v>
+        <v>26.45</v>
       </c>
       <c r="AH3">
-        <v>0.6193181818181818</v>
+        <v>0.5259631490787269</v>
       </c>
       <c r="AI3">
-        <v>0.5521783181357649</v>
+        <v>0.4937106918238993</v>
       </c>
       <c r="AJ3">
-        <v>0.6085534003271792</v>
+        <v>0.4831050228310502</v>
       </c>
       <c r="AK3">
-        <v>0.5409223099293726</v>
+        <v>0.4509803921568627</v>
       </c>
       <c r="AL3">
-        <v>9.32</v>
+        <v>7.95</v>
       </c>
       <c r="AM3">
-        <v>8.140000000000001</v>
+        <v>6.11</v>
       </c>
       <c r="AN3">
-        <v>-10.30245746691871</v>
+        <v>-3.64692218350755</v>
       </c>
       <c r="AO3">
-        <v>-0.5804721030042919</v>
+        <v>-1.09811320754717</v>
       </c>
       <c r="AP3">
-        <v>-9.844990548204159</v>
+        <v>-3.072009291521487</v>
       </c>
       <c r="AQ3">
-        <v>-0.6646191646191646</v>
+        <v>-1.428805237315875</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/argentina/argentina_homebuilding.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_homebuilding.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="base_gcdi" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.488</v>
+        <v>0.278</v>
       </c>
       <c r="G2">
-        <v>-0.05170529801324504</v>
+        <v>-0.08765017667844521</v>
       </c>
       <c r="H2">
-        <v>-0.05198675496688742</v>
+        <v>-0.08780918727915193</v>
       </c>
       <c r="I2">
-        <v>-0.1445364238410596</v>
+        <v>0.173321554770318</v>
       </c>
       <c r="J2">
-        <v>-0.1445364238410596</v>
+        <v>0.1413107694421426</v>
       </c>
       <c r="K2">
-        <v>-16.2</v>
+        <v>6.71</v>
       </c>
       <c r="L2">
-        <v>-0.2682119205298013</v>
+        <v>0.1185512367491166</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +617,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +626,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4.95</v>
+        <v>0.929</v>
       </c>
       <c r="V2">
-        <v>0.1749116607773852</v>
+        <v>0.04838541666666667</v>
       </c>
       <c r="W2">
-        <v>-0.36</v>
+        <v>0.2313793103448276</v>
       </c>
       <c r="X2">
-        <v>0.4878139353778094</v>
+        <v>0.4596731779048582</v>
       </c>
       <c r="Y2">
-        <v>-0.8478139353778094</v>
+        <v>-0.2282938675600306</v>
       </c>
       <c r="Z2">
-        <v>0.7973597359735973</v>
+        <v>1.941015089163238</v>
       </c>
       <c r="AA2">
-        <v>-0.1152475247524753</v>
+        <v>0.2742863357484662</v>
       </c>
       <c r="AB2">
-        <v>0.300241699047213</v>
+        <v>0.2552606129474822</v>
       </c>
       <c r="AC2">
-        <v>-0.4154892237996882</v>
+        <v>0.01902572280098402</v>
       </c>
       <c r="AD2">
-        <v>31.4</v>
+        <v>28.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>31.4</v>
+        <v>28.6</v>
       </c>
       <c r="AG2">
-        <v>26.45</v>
+        <v>27.671</v>
       </c>
       <c r="AH2">
-        <v>0.5259631490787269</v>
+        <v>0.598326359832636</v>
       </c>
       <c r="AI2">
-        <v>0.4937106918238993</v>
+        <v>0.5596868884540117</v>
       </c>
       <c r="AJ2">
-        <v>0.4831050228310502</v>
+        <v>0.590365044483796</v>
       </c>
       <c r="AK2">
-        <v>0.4509803921568627</v>
+        <v>0.5515337545594068</v>
       </c>
       <c r="AL2">
-        <v>7.95</v>
+        <v>0.505</v>
       </c>
       <c r="AM2">
-        <v>6.11</v>
+        <v>-1.555</v>
       </c>
       <c r="AN2">
-        <v>-3.64692218350755</v>
+        <v>2.776699029126214</v>
       </c>
       <c r="AO2">
-        <v>-1.09811320754717</v>
+        <v>19.42574257425743</v>
       </c>
       <c r="AP2">
-        <v>-3.072009291521487</v>
+        <v>2.686504854368932</v>
       </c>
       <c r="AQ2">
-        <v>-1.428805237315875</v>
+        <v>-6.308681672025723</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.488</v>
+        <v>0.278</v>
       </c>
       <c r="G3">
-        <v>-0.05170529801324504</v>
+        <v>-0.08765017667844521</v>
       </c>
       <c r="H3">
-        <v>-0.05198675496688742</v>
+        <v>-0.08780918727915193</v>
       </c>
       <c r="I3">
-        <v>-0.1445364238410596</v>
+        <v>0.173321554770318</v>
       </c>
       <c r="J3">
-        <v>-0.1445364238410596</v>
+        <v>0.1413107694421426</v>
       </c>
       <c r="K3">
-        <v>-16.2</v>
+        <v>6.71</v>
       </c>
       <c r="L3">
-        <v>-0.2682119205298013</v>
+        <v>0.1185512367491166</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +745,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +754,8851 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>4.95</v>
+        <v>0.929</v>
       </c>
       <c r="V3">
-        <v>0.1749116607773852</v>
+        <v>0.04838541666666667</v>
       </c>
       <c r="W3">
-        <v>-0.36</v>
+        <v>0.2313793103448276</v>
       </c>
       <c r="X3">
-        <v>0.4878139353778094</v>
+        <v>0.4596731779048582</v>
       </c>
       <c r="Y3">
-        <v>-0.8478139353778094</v>
+        <v>-0.2282938675600306</v>
       </c>
       <c r="Z3">
-        <v>0.7973597359735973</v>
+        <v>1.941015089163238</v>
       </c>
       <c r="AA3">
-        <v>-0.1152475247524753</v>
+        <v>0.2742863357484662</v>
       </c>
       <c r="AB3">
-        <v>0.300241699047213</v>
+        <v>0.2552606129474822</v>
       </c>
       <c r="AC3">
-        <v>-0.4154892237996882</v>
+        <v>0.01902572280098402</v>
       </c>
       <c r="AD3">
-        <v>31.4</v>
+        <v>28.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>31.4</v>
+        <v>28.6</v>
       </c>
       <c r="AG3">
-        <v>26.45</v>
+        <v>27.671</v>
       </c>
       <c r="AH3">
-        <v>0.5259631490787269</v>
+        <v>0.598326359832636</v>
       </c>
       <c r="AI3">
-        <v>0.4937106918238993</v>
+        <v>0.5596868884540117</v>
       </c>
       <c r="AJ3">
-        <v>0.4831050228310502</v>
+        <v>0.590365044483796</v>
       </c>
       <c r="AK3">
-        <v>0.4509803921568627</v>
+        <v>0.5515337545594068</v>
       </c>
       <c r="AL3">
-        <v>7.95</v>
+        <v>0.505</v>
       </c>
       <c r="AM3">
-        <v>6.11</v>
+        <v>-1.555</v>
       </c>
       <c r="AN3">
-        <v>-3.64692218350755</v>
+        <v>2.776699029126214</v>
       </c>
       <c r="AO3">
-        <v>-1.09811320754717</v>
+        <v>19.42574257425743</v>
       </c>
       <c r="AP3">
-        <v>-3.072009291521487</v>
+        <v>2.686504854368932</v>
       </c>
       <c r="AQ3">
-        <v>-1.428805237315875</v>
+        <v>-6.308681672025723</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GCDI S.A. (BASE:GCDI)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BASE:GCDI</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Homebuilding</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>19.4257425742574</v>
+      </c>
+      <c r="F2">
+        <v>3.6886682756931</v>
+      </c>
+      <c r="G2">
+        <v>2.77669902912621</v>
+      </c>
+      <c r="H2">
+        <v>4.59436893203883</v>
+      </c>
+      <c r="I2">
+        <v>0.598326359832636</v>
+      </c>
+      <c r="J2">
+        <v>0.99</v>
+      </c>
+      <c r="K2">
+        <v>19.2</v>
+      </c>
+      <c r="L2">
+        <v>27.3979355663952</v>
+      </c>
+      <c r="M2">
+        <v>46.871</v>
+      </c>
+      <c r="N2">
+        <v>73.79093556639521</v>
+      </c>
+      <c r="O2">
+        <v>28.6</v>
+      </c>
+      <c r="P2">
+        <v>47.322</v>
+      </c>
+      <c r="Q2">
+        <v>0.255260612947482</v>
+      </c>
+      <c r="R2">
+        <v>0.176292841249215</v>
+      </c>
+      <c r="S2">
+        <v>0.118032597311761</v>
+      </c>
+      <c r="T2">
+        <v>0.03653</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.459673177904858</v>
+      </c>
+      <c r="X2">
+        <v>14.0128141249215</v>
+      </c>
+      <c r="Y2">
+        <v>1.9000876978841</v>
+      </c>
+      <c r="Z2">
+        <v>63.0875373455712</v>
+      </c>
+      <c r="AA2">
+        <v>28.6</v>
+      </c>
+      <c r="AB2">
+        <v>0.1815886112488636</v>
+      </c>
+      <c r="AC2">
+        <v>19.42574257425743</v>
+      </c>
+      <c r="AD2">
+        <v>28.6</v>
+      </c>
+      <c r="AE2">
+        <v>0.505</v>
+      </c>
+      <c r="AF2">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="AG2">
+        <v>10.3</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>19.2</v>
+      </c>
+      <c r="AK2">
+        <v>0.2215019750791156</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.35</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>0.4979999999999993</v>
+      </c>
+      <c r="AR2">
+        <v>0.505</v>
+      </c>
+      <c r="AS2">
+        <v>28.6</v>
+      </c>
+      <c r="AT2">
+        <v>0.929</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.2526334219574828</v>
+      </c>
+      <c r="C2">
+        <v>48.37586446386638</v>
+      </c>
+      <c r="D2">
+        <v>47.44686446386638</v>
+      </c>
+      <c r="E2">
+        <v>-28.6</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.929</v>
+      </c>
+      <c r="H2">
+        <v>19.2</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>10.3</v>
+      </c>
+      <c r="K2">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L2">
+        <v>9.81</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>9.81</v>
+      </c>
+      <c r="O2">
+        <v>3.4335</v>
+      </c>
+      <c r="P2">
+        <v>6.3765</v>
+      </c>
+      <c r="Q2">
+        <v>6.8665</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.2526334219574828</v>
+      </c>
+      <c r="T2">
+        <v>0.9653793013859414</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.35</v>
+      </c>
+      <c r="W2">
+        <v>0.029055</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.2517875549806317</v>
+      </c>
+      <c r="C3">
+        <v>48.08629676832083</v>
+      </c>
+      <c r="D3">
+        <v>47.63529676832083</v>
+      </c>
+      <c r="E3">
+        <v>-28.122</v>
+      </c>
+      <c r="F3">
+        <v>0.478</v>
+      </c>
+      <c r="G3">
+        <v>0.929</v>
+      </c>
+      <c r="H3">
+        <v>19.2</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>10.3</v>
+      </c>
+      <c r="K3">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L3">
+        <v>9.81</v>
+      </c>
+      <c r="M3">
+        <v>0.0213666</v>
+      </c>
+      <c r="N3">
+        <v>9.7886334</v>
+      </c>
+      <c r="O3">
+        <v>3.42602169</v>
+      </c>
+      <c r="P3">
+        <v>6.36261171</v>
+      </c>
+      <c r="Q3">
+        <v>6.852611710000001</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.2540373787683148</v>
+      </c>
+      <c r="T3">
+        <v>0.971717650334435</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.35</v>
+      </c>
+      <c r="W3">
+        <v>0.029055</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>459.1277975906321</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.2509416880037805</v>
+      </c>
+      <c r="C4">
+        <v>47.79823173512523</v>
+      </c>
+      <c r="D4">
+        <v>47.82523173512523</v>
+      </c>
+      <c r="E4">
+        <v>-27.644</v>
+      </c>
+      <c r="F4">
+        <v>0.956</v>
+      </c>
+      <c r="G4">
+        <v>0.929</v>
+      </c>
+      <c r="H4">
+        <v>19.2</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>10.3</v>
+      </c>
+      <c r="K4">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L4">
+        <v>9.81</v>
+      </c>
+      <c r="M4">
+        <v>0.0427332</v>
+      </c>
+      <c r="N4">
+        <v>9.7672668</v>
+      </c>
+      <c r="O4">
+        <v>3.41854338</v>
+      </c>
+      <c r="P4">
+        <v>6.348723420000001</v>
+      </c>
+      <c r="Q4">
+        <v>6.838723420000001</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.2554699877589597</v>
+      </c>
+      <c r="T4">
+        <v>0.9781853533431019</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.35</v>
+      </c>
+      <c r="W4">
+        <v>0.029055</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>229.563898795316</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.2500958210269292</v>
+      </c>
+      <c r="C5">
+        <v>47.51168741081436</v>
+      </c>
+      <c r="D5">
+        <v>48.01668741081436</v>
+      </c>
+      <c r="E5">
+        <v>-27.166</v>
+      </c>
+      <c r="F5">
+        <v>1.434</v>
+      </c>
+      <c r="G5">
+        <v>0.929</v>
+      </c>
+      <c r="H5">
+        <v>19.2</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>10.3</v>
+      </c>
+      <c r="K5">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L5">
+        <v>9.81</v>
+      </c>
+      <c r="M5">
+        <v>0.0640998</v>
+      </c>
+      <c r="N5">
+        <v>9.745900200000001</v>
+      </c>
+      <c r="O5">
+        <v>3.41106507</v>
+      </c>
+      <c r="P5">
+        <v>6.334835130000001</v>
+      </c>
+      <c r="Q5">
+        <v>6.824835130000001</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.2569321350793085</v>
+      </c>
+      <c r="T5">
+        <v>0.9847864110529783</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.35</v>
+      </c>
+      <c r="W5">
+        <v>0.029055</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>153.0425991968774</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.2492499540500781</v>
+      </c>
+      <c r="C6">
+        <v>47.22668213206256</v>
+      </c>
+      <c r="D6">
+        <v>48.20968213206256</v>
+      </c>
+      <c r="E6">
+        <v>-26.688</v>
+      </c>
+      <c r="F6">
+        <v>1.912</v>
+      </c>
+      <c r="G6">
+        <v>0.929</v>
+      </c>
+      <c r="H6">
+        <v>19.2</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>10.3</v>
+      </c>
+      <c r="K6">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L6">
+        <v>9.81</v>
+      </c>
+      <c r="M6">
+        <v>0.0854664</v>
+      </c>
+      <c r="N6">
+        <v>9.724533600000001</v>
+      </c>
+      <c r="O6">
+        <v>3.40358676</v>
+      </c>
+      <c r="P6">
+        <v>6.320946840000001</v>
+      </c>
+      <c r="Q6">
+        <v>6.810946840000002</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.2584247438021647</v>
+      </c>
+      <c r="T6">
+        <v>0.9915249907984773</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.35</v>
+      </c>
+      <c r="W6">
+        <v>0.029055</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>114.781949397658</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.2484040870732269</v>
+      </c>
+      <c r="C7">
+        <v>46.94323453153824</v>
+      </c>
+      <c r="D7">
+        <v>48.40423453153824</v>
+      </c>
+      <c r="E7">
+        <v>-26.21</v>
+      </c>
+      <c r="F7">
+        <v>2.39</v>
+      </c>
+      <c r="G7">
+        <v>0.929</v>
+      </c>
+      <c r="H7">
+        <v>19.2</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>10.3</v>
+      </c>
+      <c r="K7">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L7">
+        <v>9.81</v>
+      </c>
+      <c r="M7">
+        <v>0.106833</v>
+      </c>
+      <c r="N7">
+        <v>9.703167000000001</v>
+      </c>
+      <c r="O7">
+        <v>3.39610845</v>
+      </c>
+      <c r="P7">
+        <v>6.307058550000001</v>
+      </c>
+      <c r="Q7">
+        <v>6.797058550000001</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.2599487758665546</v>
+      </c>
+      <c r="T7">
+        <v>0.9984054353807236</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.35</v>
+      </c>
+      <c r="W7">
+        <v>0.029055</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>91.82555951812641</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.2475582200963757</v>
+      </c>
+      <c r="C8">
+        <v>46.66136354390043</v>
+      </c>
+      <c r="D8">
+        <v>48.60036354390043</v>
+      </c>
+      <c r="E8">
+        <v>-25.732</v>
+      </c>
+      <c r="F8">
+        <v>2.868</v>
+      </c>
+      <c r="G8">
+        <v>0.929</v>
+      </c>
+      <c r="H8">
+        <v>19.2</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>10.3</v>
+      </c>
+      <c r="K8">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L8">
+        <v>9.81</v>
+      </c>
+      <c r="M8">
+        <v>0.1281996</v>
+      </c>
+      <c r="N8">
+        <v>9.6818004</v>
+      </c>
+      <c r="O8">
+        <v>3.38863014</v>
+      </c>
+      <c r="P8">
+        <v>6.29317026</v>
+      </c>
+      <c r="Q8">
+        <v>6.78317026</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.2615052341450805</v>
+      </c>
+      <c r="T8">
+        <v>1.00543227240089</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.35</v>
+      </c>
+      <c r="W8">
+        <v>0.029055</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>76.52129959843869</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.2467123531195245</v>
+      </c>
+      <c r="C9">
+        <v>46.38108841194189</v>
+      </c>
+      <c r="D9">
+        <v>48.79808841194189</v>
+      </c>
+      <c r="E9">
+        <v>-25.254</v>
+      </c>
+      <c r="F9">
+        <v>3.346</v>
+      </c>
+      <c r="G9">
+        <v>0.929</v>
+      </c>
+      <c r="H9">
+        <v>19.2</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>10.3</v>
+      </c>
+      <c r="K9">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L9">
+        <v>9.81</v>
+      </c>
+      <c r="M9">
+        <v>0.1495662</v>
+      </c>
+      <c r="N9">
+        <v>9.6604338</v>
+      </c>
+      <c r="O9">
+        <v>3.38115183</v>
+      </c>
+      <c r="P9">
+        <v>6.27928197</v>
+      </c>
+      <c r="Q9">
+        <v>6.76928197</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.26309516464465</v>
+      </c>
+      <c r="T9">
+        <v>1.012610224195684</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.35</v>
+      </c>
+      <c r="W9">
+        <v>0.029055</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>65.58968537009029</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.2458664861426734</v>
+      </c>
+      <c r="C10">
+        <v>46.10242869288277</v>
+      </c>
+      <c r="D10">
+        <v>48.99742869288277</v>
+      </c>
+      <c r="E10">
+        <v>-24.776</v>
+      </c>
+      <c r="F10">
+        <v>3.824</v>
+      </c>
+      <c r="G10">
+        <v>0.929</v>
+      </c>
+      <c r="H10">
+        <v>19.2</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>10.3</v>
+      </c>
+      <c r="K10">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L10">
+        <v>9.81</v>
+      </c>
+      <c r="M10">
+        <v>0.1709328</v>
+      </c>
+      <c r="N10">
+        <v>9.639067200000001</v>
+      </c>
+      <c r="O10">
+        <v>3.37367352</v>
+      </c>
+      <c r="P10">
+        <v>6.265393680000001</v>
+      </c>
+      <c r="Q10">
+        <v>6.755393680000001</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.2647196588507319</v>
+      </c>
+      <c r="T10">
+        <v>1.019944218420799</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.35</v>
+      </c>
+      <c r="W10">
+        <v>0.029055</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>57.39097469882902</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.2450206191658221</v>
+      </c>
+      <c r="C11">
+        <v>45.82540426481919</v>
+      </c>
+      <c r="D11">
+        <v>49.19840426481919</v>
+      </c>
+      <c r="E11">
+        <v>-24.298</v>
+      </c>
+      <c r="F11">
+        <v>4.302</v>
+      </c>
+      <c r="G11">
+        <v>0.929</v>
+      </c>
+      <c r="H11">
+        <v>19.2</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>10.3</v>
+      </c>
+      <c r="K11">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L11">
+        <v>9.81</v>
+      </c>
+      <c r="M11">
+        <v>0.1922994</v>
+      </c>
+      <c r="N11">
+        <v>9.617700600000001</v>
+      </c>
+      <c r="O11">
+        <v>3.36619521</v>
+      </c>
+      <c r="P11">
+        <v>6.25150539</v>
+      </c>
+      <c r="Q11">
+        <v>6.74150539</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.2663798562261782</v>
+      </c>
+      <c r="T11">
+        <v>1.02743939933218</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.35</v>
+      </c>
+      <c r="W11">
+        <v>0.029055</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>51.01419973229246</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.244174752188971</v>
+      </c>
+      <c r="C12">
+        <v>45.55003533333092</v>
+      </c>
+      <c r="D12">
+        <v>49.40103533333092</v>
+      </c>
+      <c r="E12">
+        <v>-23.82</v>
+      </c>
+      <c r="F12">
+        <v>4.78</v>
+      </c>
+      <c r="G12">
+        <v>0.929</v>
+      </c>
+      <c r="H12">
+        <v>19.2</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>10.3</v>
+      </c>
+      <c r="K12">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L12">
+        <v>9.81</v>
+      </c>
+      <c r="M12">
+        <v>0.213666</v>
+      </c>
+      <c r="N12">
+        <v>9.596334000000001</v>
+      </c>
+      <c r="O12">
+        <v>3.3587169</v>
+      </c>
+      <c r="P12">
+        <v>6.2376171</v>
+      </c>
+      <c r="Q12">
+        <v>6.727617100000001</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.2680769468766344</v>
+      </c>
+      <c r="T12">
+        <v>1.035101139819371</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.35</v>
+      </c>
+      <c r="W12">
+        <v>0.029055</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>45.91277975906321</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.2433288852121198</v>
+      </c>
+      <c r="C13">
+        <v>45.27634243825347</v>
+      </c>
+      <c r="D13">
+        <v>49.60534243825347</v>
+      </c>
+      <c r="E13">
+        <v>-23.342</v>
+      </c>
+      <c r="F13">
+        <v>5.258</v>
+      </c>
+      <c r="G13">
+        <v>0.929</v>
+      </c>
+      <c r="H13">
+        <v>19.2</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>10.3</v>
+      </c>
+      <c r="K13">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L13">
+        <v>9.81</v>
+      </c>
+      <c r="M13">
+        <v>0.2350326</v>
+      </c>
+      <c r="N13">
+        <v>9.5749674</v>
+      </c>
+      <c r="O13">
+        <v>3.35123859</v>
+      </c>
+      <c r="P13">
+        <v>6.223728810000001</v>
+      </c>
+      <c r="Q13">
+        <v>6.713728810000001</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.2698121743956402</v>
+      </c>
+      <c r="T13">
+        <v>1.042935054250093</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.35</v>
+      </c>
+      <c r="W13">
+        <v>0.029055</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>41.73889069005747</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.2424830182352685</v>
+      </c>
+      <c r="C14">
+        <v>45.00434646061851</v>
+      </c>
+      <c r="D14">
+        <v>49.8113464606185</v>
+      </c>
+      <c r="E14">
+        <v>-22.864</v>
+      </c>
+      <c r="F14">
+        <v>5.736</v>
+      </c>
+      <c r="G14">
+        <v>0.929</v>
+      </c>
+      <c r="H14">
+        <v>19.2</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>10.3</v>
+      </c>
+      <c r="K14">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L14">
+        <v>9.81</v>
+      </c>
+      <c r="M14">
+        <v>0.2563992</v>
+      </c>
+      <c r="N14">
+        <v>9.5536008</v>
+      </c>
+      <c r="O14">
+        <v>3.34376028</v>
+      </c>
+      <c r="P14">
+        <v>6.20984052</v>
+      </c>
+      <c r="Q14">
+        <v>6.69984052</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.2715868389037143</v>
+      </c>
+      <c r="T14">
+        <v>1.050947012190604</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.35</v>
+      </c>
+      <c r="W14">
+        <v>0.029055</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>38.26064979921934</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.2416371512584174</v>
+      </c>
+      <c r="C15">
+        <v>44.73406862976814</v>
+      </c>
+      <c r="D15">
+        <v>50.01906862976814</v>
+      </c>
+      <c r="E15">
+        <v>-22.386</v>
+      </c>
+      <c r="F15">
+        <v>6.214</v>
+      </c>
+      <c r="G15">
+        <v>0.929</v>
+      </c>
+      <c r="H15">
+        <v>19.2</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>10.3</v>
+      </c>
+      <c r="K15">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L15">
+        <v>9.81</v>
+      </c>
+      <c r="M15">
+        <v>0.2777658</v>
+      </c>
+      <c r="N15">
+        <v>9.532234200000001</v>
+      </c>
+      <c r="O15">
+        <v>3.33628197</v>
+      </c>
+      <c r="P15">
+        <v>6.195952230000001</v>
+      </c>
+      <c r="Q15">
+        <v>6.685952230000002</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.2734023002970314</v>
+      </c>
+      <c r="T15">
+        <v>1.059143153072277</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.35</v>
+      </c>
+      <c r="W15">
+        <v>0.029055</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>35.31752289158709</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.2407912842815662</v>
+      </c>
+      <c r="C16">
+        <v>44.46553053064796</v>
+      </c>
+      <c r="D16">
+        <v>50.22853053064796</v>
+      </c>
+      <c r="E16">
+        <v>-21.908</v>
+      </c>
+      <c r="F16">
+        <v>6.692</v>
+      </c>
+      <c r="G16">
+        <v>0.929</v>
+      </c>
+      <c r="H16">
+        <v>19.2</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>10.3</v>
+      </c>
+      <c r="K16">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L16">
+        <v>9.81</v>
+      </c>
+      <c r="M16">
+        <v>0.2991324</v>
+      </c>
+      <c r="N16">
+        <v>9.510867600000001</v>
+      </c>
+      <c r="O16">
+        <v>3.32880366</v>
+      </c>
+      <c r="P16">
+        <v>6.182063940000001</v>
+      </c>
+      <c r="Q16">
+        <v>6.672063940000001</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.2752599817227513</v>
+      </c>
+      <c r="T16">
+        <v>1.067529901881431</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.35</v>
+      </c>
+      <c r="W16">
+        <v>0.029055</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>32.79484268504515</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.239945417304715</v>
+      </c>
+      <c r="C17">
+        <v>44.198754111284</v>
+      </c>
+      <c r="D17">
+        <v>50.439754111284</v>
+      </c>
+      <c r="E17">
+        <v>-21.43</v>
+      </c>
+      <c r="F17">
+        <v>7.169999999999999</v>
+      </c>
+      <c r="G17">
+        <v>0.929</v>
+      </c>
+      <c r="H17">
+        <v>19.2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>10.3</v>
+      </c>
+      <c r="K17">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L17">
+        <v>9.81</v>
+      </c>
+      <c r="M17">
+        <v>0.320499</v>
+      </c>
+      <c r="N17">
+        <v>9.489501000000001</v>
+      </c>
+      <c r="O17">
+        <v>3.32132535</v>
+      </c>
+      <c r="P17">
+        <v>6.16817565</v>
+      </c>
+      <c r="Q17">
+        <v>6.65817565</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.2771613732996647</v>
+      </c>
+      <c r="T17">
+        <v>1.076113985956682</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.35</v>
+      </c>
+      <c r="W17">
+        <v>0.029055</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>30.60851983937548</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.2390995503278638</v>
+      </c>
+      <c r="C18">
+        <v>43.93376169044929</v>
+      </c>
+      <c r="D18">
+        <v>50.65276169044928</v>
+      </c>
+      <c r="E18">
+        <v>-20.952</v>
+      </c>
+      <c r="F18">
+        <v>7.648</v>
+      </c>
+      <c r="G18">
+        <v>0.929</v>
+      </c>
+      <c r="H18">
+        <v>19.2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>10.3</v>
+      </c>
+      <c r="K18">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L18">
+        <v>9.81</v>
+      </c>
+      <c r="M18">
+        <v>0.3418656</v>
+      </c>
+      <c r="N18">
+        <v>9.4681344</v>
+      </c>
+      <c r="O18">
+        <v>3.31384704</v>
+      </c>
+      <c r="P18">
+        <v>6.154287360000001</v>
+      </c>
+      <c r="Q18">
+        <v>6.644287360000001</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.2791080361045998</v>
+      </c>
+      <c r="T18">
+        <v>1.084902452986106</v>
+      </c>
+      <c r="U18">
+        <v>0.0447</v>
+      </c>
+      <c r="V18">
+        <v>0.35</v>
+      </c>
+      <c r="W18">
+        <v>0.029055</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>28.69548734941451</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.2382536833510127</v>
+      </c>
+      <c r="C19">
+        <v>43.67057596552517</v>
+      </c>
+      <c r="D19">
+        <v>50.86757596552516</v>
+      </c>
+      <c r="E19">
+        <v>-20.474</v>
+      </c>
+      <c r="F19">
+        <v>8.125999999999999</v>
+      </c>
+      <c r="G19">
+        <v>0.929</v>
+      </c>
+      <c r="H19">
+        <v>19.2</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>10.3</v>
+      </c>
+      <c r="K19">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L19">
+        <v>9.81</v>
+      </c>
+      <c r="M19">
+        <v>0.3632322</v>
+      </c>
+      <c r="N19">
+        <v>9.4467678</v>
+      </c>
+      <c r="O19">
+        <v>3.30636873</v>
+      </c>
+      <c r="P19">
+        <v>6.14039907</v>
+      </c>
+      <c r="Q19">
+        <v>6.63039907</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.2811016064470032</v>
+      </c>
+      <c r="T19">
+        <v>1.093902690305395</v>
+      </c>
+      <c r="U19">
+        <v>0.0447</v>
+      </c>
+      <c r="V19">
+        <v>0.35</v>
+      </c>
+      <c r="W19">
+        <v>0.029055</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>27.0075175053313</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.2374078163741614</v>
+      </c>
+      <c r="C20">
+        <v>43.40922002056401</v>
+      </c>
+      <c r="D20">
+        <v>51.084220020564</v>
+      </c>
+      <c r="E20">
+        <v>-19.996</v>
+      </c>
+      <c r="F20">
+        <v>8.603999999999999</v>
+      </c>
+      <c r="G20">
+        <v>0.929</v>
+      </c>
+      <c r="H20">
+        <v>19.2</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>10.3</v>
+      </c>
+      <c r="K20">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L20">
+        <v>9.81</v>
+      </c>
+      <c r="M20">
+        <v>0.3845988</v>
+      </c>
+      <c r="N20">
+        <v>9.4254012</v>
+      </c>
+      <c r="O20">
+        <v>3.29889042</v>
+      </c>
+      <c r="P20">
+        <v>6.12651078</v>
+      </c>
+      <c r="Q20">
+        <v>6.61651078</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.2831438004562944</v>
+      </c>
+      <c r="T20">
+        <v>1.103122445608082</v>
+      </c>
+      <c r="U20">
+        <v>0.0447</v>
+      </c>
+      <c r="V20">
+        <v>0.35</v>
+      </c>
+      <c r="W20">
+        <v>0.029055</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>25.50709986614623</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.2365619493973103</v>
+      </c>
+      <c r="C21">
+        <v>43.14971733455833</v>
+      </c>
+      <c r="D21">
+        <v>51.30271733455833</v>
+      </c>
+      <c r="E21">
+        <v>-19.518</v>
+      </c>
+      <c r="F21">
+        <v>9.081999999999999</v>
+      </c>
+      <c r="G21">
+        <v>0.929</v>
+      </c>
+      <c r="H21">
+        <v>19.2</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>10.3</v>
+      </c>
+      <c r="K21">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L21">
+        <v>9.81</v>
+      </c>
+      <c r="M21">
+        <v>0.4059654</v>
+      </c>
+      <c r="N21">
+        <v>9.404034600000001</v>
+      </c>
+      <c r="O21">
+        <v>3.29141211</v>
+      </c>
+      <c r="P21">
+        <v>6.112622490000001</v>
+      </c>
+      <c r="Q21">
+        <v>6.602622490000002</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.285236419009025</v>
+      </c>
+      <c r="T21">
+        <v>1.112569849189847</v>
+      </c>
+      <c r="U21">
+        <v>0.0447</v>
+      </c>
+      <c r="V21">
+        <v>0.35</v>
+      </c>
+      <c r="W21">
+        <v>0.029055</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>24.16462092582275</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.2357160824204591</v>
+      </c>
+      <c r="C22">
+        <v>42.89209178992341</v>
+      </c>
+      <c r="D22">
+        <v>51.52309178992341</v>
+      </c>
+      <c r="E22">
+        <v>-19.04</v>
+      </c>
+      <c r="F22">
+        <v>9.56</v>
+      </c>
+      <c r="G22">
+        <v>0.929</v>
+      </c>
+      <c r="H22">
+        <v>19.2</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>10.3</v>
+      </c>
+      <c r="K22">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L22">
+        <v>9.81</v>
+      </c>
+      <c r="M22">
+        <v>0.427332</v>
+      </c>
+      <c r="N22">
+        <v>9.382668000000001</v>
+      </c>
+      <c r="O22">
+        <v>3.2839338</v>
+      </c>
+      <c r="P22">
+        <v>6.098734200000001</v>
+      </c>
+      <c r="Q22">
+        <v>6.588734200000001</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.2873813530255739</v>
+      </c>
+      <c r="T22">
+        <v>1.122253437861157</v>
+      </c>
+      <c r="U22">
+        <v>0.0447</v>
+      </c>
+      <c r="V22">
+        <v>0.35</v>
+      </c>
+      <c r="W22">
+        <v>0.029055</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>22.95638987953161</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.2348702154436079</v>
+      </c>
+      <c r="C23">
+        <v>42.63636768119923</v>
+      </c>
+      <c r="D23">
+        <v>51.74536768119923</v>
+      </c>
+      <c r="E23">
+        <v>-18.562</v>
+      </c>
+      <c r="F23">
+        <v>10.038</v>
+      </c>
+      <c r="G23">
+        <v>0.929</v>
+      </c>
+      <c r="H23">
+        <v>19.2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>10.3</v>
+      </c>
+      <c r="K23">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L23">
+        <v>9.81</v>
+      </c>
+      <c r="M23">
+        <v>0.4486985999999999</v>
+      </c>
+      <c r="N23">
+        <v>9.3613014</v>
+      </c>
+      <c r="O23">
+        <v>3.27645549</v>
+      </c>
+      <c r="P23">
+        <v>6.08484591</v>
+      </c>
+      <c r="Q23">
+        <v>6.574845910000001</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.2895805891691239</v>
+      </c>
+      <c r="T23">
+        <v>1.132182180676044</v>
+      </c>
+      <c r="U23">
+        <v>0.0447</v>
+      </c>
+      <c r="V23">
+        <v>0.35</v>
+      </c>
+      <c r="W23">
+        <v>0.029055</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>21.86322845669677</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.2340243484667567</v>
+      </c>
+      <c r="C24">
+        <v>42.38256972397877</v>
+      </c>
+      <c r="D24">
+        <v>51.96956972397876</v>
+      </c>
+      <c r="E24">
+        <v>-18.084</v>
+      </c>
+      <c r="F24">
+        <v>10.516</v>
+      </c>
+      <c r="G24">
+        <v>0.929</v>
+      </c>
+      <c r="H24">
+        <v>19.2</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>10.3</v>
+      </c>
+      <c r="K24">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L24">
+        <v>9.81</v>
+      </c>
+      <c r="M24">
+        <v>0.4700652</v>
+      </c>
+      <c r="N24">
+        <v>9.3399348</v>
+      </c>
+      <c r="O24">
+        <v>3.26897718</v>
+      </c>
+      <c r="P24">
+        <v>6.07095762</v>
+      </c>
+      <c r="Q24">
+        <v>6.56095762</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.2918362159830213</v>
+      </c>
+      <c r="T24">
+        <v>1.142365506640031</v>
+      </c>
+      <c r="U24">
+        <v>0.0447</v>
+      </c>
+      <c r="V24">
+        <v>0.35</v>
+      </c>
+      <c r="W24">
+        <v>0.029055</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>20.86944534502873</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.2331784814899055</v>
+      </c>
+      <c r="C25">
+        <v>42.13072306406934</v>
+      </c>
+      <c r="D25">
+        <v>52.19572306406934</v>
+      </c>
+      <c r="E25">
+        <v>-17.606</v>
+      </c>
+      <c r="F25">
+        <v>10.994</v>
+      </c>
+      <c r="G25">
+        <v>0.929</v>
+      </c>
+      <c r="H25">
+        <v>19.2</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>10.3</v>
+      </c>
+      <c r="K25">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L25">
+        <v>9.81</v>
+      </c>
+      <c r="M25">
+        <v>0.4914318</v>
+      </c>
+      <c r="N25">
+        <v>9.3185682</v>
+      </c>
+      <c r="O25">
+        <v>3.26149887</v>
+      </c>
+      <c r="P25">
+        <v>6.05706933</v>
+      </c>
+      <c r="Q25">
+        <v>6.54706933</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.2941504305063708</v>
+      </c>
+      <c r="T25">
+        <v>1.152813334577108</v>
+      </c>
+      <c r="U25">
+        <v>0.0447</v>
+      </c>
+      <c r="V25">
+        <v>0.35</v>
+      </c>
+      <c r="W25">
+        <v>0.029055</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>19.96207815611444</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.2323326145130543</v>
+      </c>
+      <c r="C26">
+        <v>41.88085328689434</v>
+      </c>
+      <c r="D26">
+        <v>52.42385328689434</v>
+      </c>
+      <c r="E26">
+        <v>-17.128</v>
+      </c>
+      <c r="F26">
+        <v>11.472</v>
+      </c>
+      <c r="G26">
+        <v>0.929</v>
+      </c>
+      <c r="H26">
+        <v>19.2</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>10.3</v>
+      </c>
+      <c r="K26">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L26">
+        <v>9.81</v>
+      </c>
+      <c r="M26">
+        <v>0.5127984</v>
+      </c>
+      <c r="N26">
+        <v>9.297201600000001</v>
+      </c>
+      <c r="O26">
+        <v>3.25402056</v>
+      </c>
+      <c r="P26">
+        <v>6.04318104</v>
+      </c>
+      <c r="Q26">
+        <v>6.533181040000001</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.2965255454119136</v>
+      </c>
+      <c r="T26">
+        <v>1.163536105354635</v>
+      </c>
+      <c r="U26">
+        <v>0.0447</v>
+      </c>
+      <c r="V26">
+        <v>0.35</v>
+      </c>
+      <c r="W26">
+        <v>0.029055</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>19.13032489960967</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.2314867475362031</v>
+      </c>
+      <c r="C27">
+        <v>41.63298642714231</v>
+      </c>
+      <c r="D27">
+        <v>52.65398642714231</v>
+      </c>
+      <c r="E27">
+        <v>-16.65</v>
+      </c>
+      <c r="F27">
+        <v>11.95</v>
+      </c>
+      <c r="G27">
+        <v>0.929</v>
+      </c>
+      <c r="H27">
+        <v>19.2</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>10.3</v>
+      </c>
+      <c r="K27">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L27">
+        <v>9.81</v>
+      </c>
+      <c r="M27">
+        <v>0.534165</v>
+      </c>
+      <c r="N27">
+        <v>9.275835000000001</v>
+      </c>
+      <c r="O27">
+        <v>3.24654225</v>
+      </c>
+      <c r="P27">
+        <v>6.029292750000001</v>
+      </c>
+      <c r="Q27">
+        <v>6.519292750000001</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.2989639967149375</v>
+      </c>
+      <c r="T27">
+        <v>1.174544816686229</v>
+      </c>
+      <c r="U27">
+        <v>0.0447</v>
+      </c>
+      <c r="V27">
+        <v>0.35</v>
+      </c>
+      <c r="W27">
+        <v>0.029055</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>18.36511190362529</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.2306408805593519</v>
+      </c>
+      <c r="C28">
+        <v>41.38714897867165</v>
+      </c>
+      <c r="D28">
+        <v>52.88614897867164</v>
+      </c>
+      <c r="E28">
+        <v>-16.172</v>
+      </c>
+      <c r="F28">
+        <v>12.428</v>
+      </c>
+      <c r="G28">
+        <v>0.929</v>
+      </c>
+      <c r="H28">
+        <v>19.2</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>10.3</v>
+      </c>
+      <c r="K28">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L28">
+        <v>9.81</v>
+      </c>
+      <c r="M28">
+        <v>0.5555316</v>
+      </c>
+      <c r="N28">
+        <v>9.2544684</v>
+      </c>
+      <c r="O28">
+        <v>3.23906394</v>
+      </c>
+      <c r="P28">
+        <v>6.015404460000001</v>
+      </c>
+      <c r="Q28">
+        <v>6.505404460000001</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.3014683521072323</v>
+      </c>
+      <c r="T28">
+        <v>1.185851060756514</v>
+      </c>
+      <c r="U28">
+        <v>0.0447</v>
+      </c>
+      <c r="V28">
+        <v>0.35</v>
+      </c>
+      <c r="W28">
+        <v>0.029055</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>17.65876144579354</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.2297950135825007</v>
+      </c>
+      <c r="C29">
+        <v>41.14336790467814</v>
+      </c>
+      <c r="D29">
+        <v>53.12036790467814</v>
+      </c>
+      <c r="E29">
+        <v>-15.694</v>
+      </c>
+      <c r="F29">
+        <v>12.906</v>
+      </c>
+      <c r="G29">
+        <v>0.929</v>
+      </c>
+      <c r="H29">
+        <v>19.2</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>10.3</v>
+      </c>
+      <c r="K29">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L29">
+        <v>9.81</v>
+      </c>
+      <c r="M29">
+        <v>0.5768982</v>
+      </c>
+      <c r="N29">
+        <v>9.2331018</v>
+      </c>
+      <c r="O29">
+        <v>3.23158563</v>
+      </c>
+      <c r="P29">
+        <v>6.00151617</v>
+      </c>
+      <c r="Q29">
+        <v>6.491516170000001</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.3040413199760284</v>
+      </c>
+      <c r="T29">
+        <v>1.197467064938315</v>
+      </c>
+      <c r="U29">
+        <v>0.0447</v>
+      </c>
+      <c r="V29">
+        <v>0.35</v>
+      </c>
+      <c r="W29">
+        <v>0.029055</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>17.00473324409748</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.2289491466056496</v>
+      </c>
+      <c r="C30">
+        <v>40.90167064813424</v>
+      </c>
+      <c r="D30">
+        <v>53.35667064813424</v>
+      </c>
+      <c r="E30">
+        <v>-15.216</v>
+      </c>
+      <c r="F30">
+        <v>13.384</v>
+      </c>
+      <c r="G30">
+        <v>0.929</v>
+      </c>
+      <c r="H30">
+        <v>19.2</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>10.3</v>
+      </c>
+      <c r="K30">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L30">
+        <v>9.81</v>
+      </c>
+      <c r="M30">
+        <v>0.5982648</v>
+      </c>
+      <c r="N30">
+        <v>9.2117352</v>
+      </c>
+      <c r="O30">
+        <v>3.22410732</v>
+      </c>
+      <c r="P30">
+        <v>5.98762788</v>
+      </c>
+      <c r="Q30">
+        <v>6.47762788</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.3066857591745132</v>
+      </c>
+      <c r="T30">
+        <v>1.209405735902943</v>
+      </c>
+      <c r="U30">
+        <v>0.0447</v>
+      </c>
+      <c r="V30">
+        <v>0.35</v>
+      </c>
+      <c r="W30">
+        <v>0.029055</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>16.39742134252257</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.2281032796287983</v>
+      </c>
+      <c r="C31">
+        <v>40.66208514250795</v>
+      </c>
+      <c r="D31">
+        <v>53.59508514250795</v>
+      </c>
+      <c r="E31">
+        <v>-14.738</v>
+      </c>
+      <c r="F31">
+        <v>13.862</v>
+      </c>
+      <c r="G31">
+        <v>0.929</v>
+      </c>
+      <c r="H31">
+        <v>19.2</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>10.3</v>
+      </c>
+      <c r="K31">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L31">
+        <v>9.81</v>
+      </c>
+      <c r="M31">
+        <v>0.6196313999999999</v>
+      </c>
+      <c r="N31">
+        <v>9.190368600000001</v>
+      </c>
+      <c r="O31">
+        <v>3.21662901</v>
+      </c>
+      <c r="P31">
+        <v>5.973739590000001</v>
+      </c>
+      <c r="Q31">
+        <v>6.463739590000001</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.3094046896180258</v>
+      </c>
+      <c r="T31">
+        <v>1.221680707458124</v>
+      </c>
+      <c r="U31">
+        <v>0.0447</v>
+      </c>
+      <c r="V31">
+        <v>0.35</v>
+      </c>
+      <c r="W31">
+        <v>0.029055</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>15.83199302036663</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.2272574126519471</v>
+      </c>
+      <c r="C32">
+        <v>40.4246398227704</v>
+      </c>
+      <c r="D32">
+        <v>53.8356398227704</v>
+      </c>
+      <c r="E32">
+        <v>-14.26</v>
+      </c>
+      <c r="F32">
+        <v>14.34</v>
+      </c>
+      <c r="G32">
+        <v>0.929</v>
+      </c>
+      <c r="H32">
+        <v>19.2</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>10.3</v>
+      </c>
+      <c r="K32">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L32">
+        <v>9.81</v>
+      </c>
+      <c r="M32">
+        <v>0.640998</v>
+      </c>
+      <c r="N32">
+        <v>9.169002000000001</v>
+      </c>
+      <c r="O32">
+        <v>3.2091507</v>
+      </c>
+      <c r="P32">
+        <v>5.9598513</v>
+      </c>
+      <c r="Q32">
+        <v>6.449851300000001</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.3122013037884959</v>
+      </c>
+      <c r="T32">
+        <v>1.234306392486311</v>
+      </c>
+      <c r="U32">
+        <v>0.0447</v>
+      </c>
+      <c r="V32">
+        <v>0.35</v>
+      </c>
+      <c r="W32">
+        <v>0.029055</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>15.30425991968774</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.2264115456750959</v>
+      </c>
+      <c r="C33">
+        <v>40.18936363670132</v>
+      </c>
+      <c r="D33">
+        <v>54.07836363670132</v>
+      </c>
+      <c r="E33">
+        <v>-13.782</v>
+      </c>
+      <c r="F33">
+        <v>14.818</v>
+      </c>
+      <c r="G33">
+        <v>0.929</v>
+      </c>
+      <c r="H33">
+        <v>19.2</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>10.3</v>
+      </c>
+      <c r="K33">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L33">
+        <v>9.81</v>
+      </c>
+      <c r="M33">
+        <v>0.6623646000000001</v>
+      </c>
+      <c r="N33">
+        <v>9.1476354</v>
+      </c>
+      <c r="O33">
+        <v>3.20167239</v>
+      </c>
+      <c r="P33">
+        <v>5.94596301</v>
+      </c>
+      <c r="Q33">
+        <v>6.43596301</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.3150789792392695</v>
+      </c>
+      <c r="T33">
+        <v>1.247298039399372</v>
+      </c>
+      <c r="U33">
+        <v>0.0447</v>
+      </c>
+      <c r="V33">
+        <v>0.35</v>
+      </c>
+      <c r="W33">
+        <v>0.029055</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>14.81057411582684</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.2255656786982447</v>
+      </c>
+      <c r="C34">
+        <v>39.95628605650172</v>
+      </c>
+      <c r="D34">
+        <v>54.32328605650172</v>
+      </c>
+      <c r="E34">
+        <v>-13.304</v>
+      </c>
+      <c r="F34">
+        <v>15.296</v>
+      </c>
+      <c r="G34">
+        <v>0.929</v>
+      </c>
+      <c r="H34">
+        <v>19.2</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>10.3</v>
+      </c>
+      <c r="K34">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L34">
+        <v>9.81</v>
+      </c>
+      <c r="M34">
+        <v>0.6837312</v>
+      </c>
+      <c r="N34">
+        <v>9.1262688</v>
+      </c>
+      <c r="O34">
+        <v>3.19419408</v>
+      </c>
+      <c r="P34">
+        <v>5.93207472</v>
+      </c>
+      <c r="Q34">
+        <v>6.42207472</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.3180412922033011</v>
+      </c>
+      <c r="T34">
+        <v>1.260671793574582</v>
+      </c>
+      <c r="U34">
+        <v>0.0447</v>
+      </c>
+      <c r="V34">
+        <v>0.35</v>
+      </c>
+      <c r="W34">
+        <v>0.029055</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>14.34774367470725</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.2247198117213935</v>
+      </c>
+      <c r="C35">
+        <v>39.72543709072335</v>
+      </c>
+      <c r="D35">
+        <v>54.57043709072335</v>
+      </c>
+      <c r="E35">
+        <v>-12.826</v>
+      </c>
+      <c r="F35">
+        <v>15.774</v>
+      </c>
+      <c r="G35">
+        <v>0.929</v>
+      </c>
+      <c r="H35">
+        <v>19.2</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>10.3</v>
+      </c>
+      <c r="K35">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L35">
+        <v>9.81</v>
+      </c>
+      <c r="M35">
+        <v>0.7050978</v>
+      </c>
+      <c r="N35">
+        <v>9.1049022</v>
+      </c>
+      <c r="O35">
+        <v>3.18671577</v>
+      </c>
+      <c r="P35">
+        <v>5.91818643</v>
+      </c>
+      <c r="Q35">
+        <v>6.408186430000001</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.3210920324199904</v>
+      </c>
+      <c r="T35">
+        <v>1.274444764292336</v>
+      </c>
+      <c r="U35">
+        <v>0.0447</v>
+      </c>
+      <c r="V35">
+        <v>0.35</v>
+      </c>
+      <c r="W35">
+        <v>0.029055</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>13.91296356335249</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.2238739447445424</v>
+      </c>
+      <c r="C36">
+        <v>39.49684729652564</v>
+      </c>
+      <c r="D36">
+        <v>54.81984729652564</v>
+      </c>
+      <c r="E36">
+        <v>-12.348</v>
+      </c>
+      <c r="F36">
+        <v>16.252</v>
+      </c>
+      <c r="G36">
+        <v>0.929</v>
+      </c>
+      <c r="H36">
+        <v>19.2</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>10.3</v>
+      </c>
+      <c r="K36">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L36">
+        <v>9.81</v>
+      </c>
+      <c r="M36">
+        <v>0.7264644</v>
+      </c>
+      <c r="N36">
+        <v>9.083535600000001</v>
+      </c>
+      <c r="O36">
+        <v>3.17923746</v>
+      </c>
+      <c r="P36">
+        <v>5.904298140000001</v>
+      </c>
+      <c r="Q36">
+        <v>6.394298140000001</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.3242352193099127</v>
+      </c>
+      <c r="T36">
+        <v>1.288635097759113</v>
+      </c>
+      <c r="U36">
+        <v>0.0447</v>
+      </c>
+      <c r="V36">
+        <v>0.35</v>
+      </c>
+      <c r="W36">
+        <v>0.029055</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>13.50375875266565</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.2230280777676912</v>
+      </c>
+      <c r="C37">
+        <v>39.27054779226999</v>
+      </c>
+      <c r="D37">
+        <v>55.07154779227</v>
+      </c>
+      <c r="E37">
+        <v>-11.87</v>
+      </c>
+      <c r="F37">
+        <v>16.73</v>
+      </c>
+      <c r="G37">
+        <v>0.929</v>
+      </c>
+      <c r="H37">
+        <v>19.2</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>10.3</v>
+      </c>
+      <c r="K37">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L37">
+        <v>9.81</v>
+      </c>
+      <c r="M37">
+        <v>0.7478310000000001</v>
+      </c>
+      <c r="N37">
+        <v>9.062169000000001</v>
+      </c>
+      <c r="O37">
+        <v>3.17175915</v>
+      </c>
+      <c r="P37">
+        <v>5.890409850000001</v>
+      </c>
+      <c r="Q37">
+        <v>6.380409850000001</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.3274751196426018</v>
+      </c>
+      <c r="T37">
+        <v>1.303262056871021</v>
+      </c>
+      <c r="U37">
+        <v>0.0447</v>
+      </c>
+      <c r="V37">
+        <v>0.35</v>
+      </c>
+      <c r="W37">
+        <v>0.029055</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>13.11793707401806</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.22243961079084</v>
+      </c>
+      <c r="C38">
+        <v>38.96902272107357</v>
+      </c>
+      <c r="D38">
+        <v>55.24802272107357</v>
+      </c>
+      <c r="E38">
+        <v>-11.392</v>
+      </c>
+      <c r="F38">
+        <v>17.208</v>
+      </c>
+      <c r="G38">
+        <v>0.929</v>
+      </c>
+      <c r="H38">
+        <v>19.2</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>10.3</v>
+      </c>
+      <c r="K38">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L38">
+        <v>9.81</v>
+      </c>
+      <c r="M38">
+        <v>0.7881263999999999</v>
+      </c>
+      <c r="N38">
+        <v>9.021873600000001</v>
+      </c>
+      <c r="O38">
+        <v>3.15765576</v>
+      </c>
+      <c r="P38">
+        <v>5.86421784</v>
+      </c>
+      <c r="Q38">
+        <v>6.35421784</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.3308162668606875</v>
+      </c>
+      <c r="T38">
+        <v>1.318346108455176</v>
+      </c>
+      <c r="U38">
+        <v>0.0458</v>
+      </c>
+      <c r="V38">
+        <v>0.35</v>
+      </c>
+      <c r="W38">
+        <v>0.02977</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>12.44724196524822</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2216008938139888</v>
+      </c>
+      <c r="C39">
+        <v>38.74450865118494</v>
+      </c>
+      <c r="D39">
+        <v>55.50150865118494</v>
+      </c>
+      <c r="E39">
+        <v>-10.914</v>
+      </c>
+      <c r="F39">
+        <v>17.686</v>
+      </c>
+      <c r="G39">
+        <v>0.929</v>
+      </c>
+      <c r="H39">
+        <v>19.2</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>10.3</v>
+      </c>
+      <c r="K39">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L39">
+        <v>9.81</v>
+      </c>
+      <c r="M39">
+        <v>0.8100188</v>
+      </c>
+      <c r="N39">
+        <v>8.999981200000001</v>
+      </c>
+      <c r="O39">
+        <v>3.14999342</v>
+      </c>
+      <c r="P39">
+        <v>5.849987780000001</v>
+      </c>
+      <c r="Q39">
+        <v>6.339987780000001</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.3342634822444266</v>
+      </c>
+      <c r="T39">
+        <v>1.333909018819781</v>
+      </c>
+      <c r="U39">
+        <v>0.0458</v>
+      </c>
+      <c r="V39">
+        <v>0.35</v>
+      </c>
+      <c r="W39">
+        <v>0.02977</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>12.11083002024151</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2207621768371376</v>
+      </c>
+      <c r="C40">
+        <v>38.52233136311185</v>
+      </c>
+      <c r="D40">
+        <v>55.75733136311184</v>
+      </c>
+      <c r="E40">
+        <v>-10.436</v>
+      </c>
+      <c r="F40">
+        <v>18.164</v>
+      </c>
+      <c r="G40">
+        <v>0.929</v>
+      </c>
+      <c r="H40">
+        <v>19.2</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>10.3</v>
+      </c>
+      <c r="K40">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L40">
+        <v>9.81</v>
+      </c>
+      <c r="M40">
+        <v>0.8319112</v>
+      </c>
+      <c r="N40">
+        <v>8.9780888</v>
+      </c>
+      <c r="O40">
+        <v>3.14233108</v>
+      </c>
+      <c r="P40">
+        <v>5.83575772</v>
+      </c>
+      <c r="Q40">
+        <v>6.32575772</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.3378218981244155</v>
+      </c>
+      <c r="T40">
+        <v>1.349973958550986</v>
+      </c>
+      <c r="U40">
+        <v>0.0458</v>
+      </c>
+      <c r="V40">
+        <v>0.35</v>
+      </c>
+      <c r="W40">
+        <v>0.02977</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>11.79212396707726</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2199234598602864</v>
+      </c>
+      <c r="C41">
+        <v>38.30252331921865</v>
+      </c>
+      <c r="D41">
+        <v>56.01552331921864</v>
+      </c>
+      <c r="E41">
+        <v>-9.958000000000002</v>
+      </c>
+      <c r="F41">
+        <v>18.642</v>
+      </c>
+      <c r="G41">
+        <v>0.929</v>
+      </c>
+      <c r="H41">
+        <v>19.2</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>10.3</v>
+      </c>
+      <c r="K41">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L41">
+        <v>9.81</v>
+      </c>
+      <c r="M41">
+        <v>0.8538036</v>
+      </c>
+      <c r="N41">
+        <v>8.9561964</v>
+      </c>
+      <c r="O41">
+        <v>3.13466874</v>
+      </c>
+      <c r="P41">
+        <v>5.82152766</v>
+      </c>
+      <c r="Q41">
+        <v>6.31152766</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.3414969833775188</v>
+      </c>
+      <c r="T41">
+        <v>1.36656561761764</v>
+      </c>
+      <c r="U41">
+        <v>0.0458</v>
+      </c>
+      <c r="V41">
+        <v>0.35</v>
+      </c>
+      <c r="W41">
+        <v>0.02977</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>11.48976181407527</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2190847428834352</v>
+      </c>
+      <c r="C42">
+        <v>38.08511758595262</v>
+      </c>
+      <c r="D42">
+        <v>56.27611758595262</v>
+      </c>
+      <c r="E42">
+        <v>-9.48</v>
+      </c>
+      <c r="F42">
+        <v>19.12</v>
+      </c>
+      <c r="G42">
+        <v>0.929</v>
+      </c>
+      <c r="H42">
+        <v>19.2</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>10.3</v>
+      </c>
+      <c r="K42">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L42">
+        <v>9.81</v>
+      </c>
+      <c r="M42">
+        <v>0.875696</v>
+      </c>
+      <c r="N42">
+        <v>8.934304000000001</v>
+      </c>
+      <c r="O42">
+        <v>3.1270064</v>
+      </c>
+      <c r="P42">
+        <v>5.807297600000001</v>
+      </c>
+      <c r="Q42">
+        <v>6.297297600000001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.3452945714723921</v>
+      </c>
+      <c r="T42">
+        <v>1.383710331986516</v>
+      </c>
+      <c r="U42">
+        <v>0.0458</v>
+      </c>
+      <c r="V42">
+        <v>0.35</v>
+      </c>
+      <c r="W42">
+        <v>0.02977</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>11.20251776872339</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2182460259065841</v>
+      </c>
+      <c r="C43">
+        <v>37.87014784796123</v>
+      </c>
+      <c r="D43">
+        <v>56.53914784796122</v>
+      </c>
+      <c r="E43">
+        <v>-9.002000000000002</v>
+      </c>
+      <c r="F43">
+        <v>19.598</v>
+      </c>
+      <c r="G43">
+        <v>0.929</v>
+      </c>
+      <c r="H43">
+        <v>19.2</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>10.3</v>
+      </c>
+      <c r="K43">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L43">
+        <v>9.81</v>
+      </c>
+      <c r="M43">
+        <v>0.8975884</v>
+      </c>
+      <c r="N43">
+        <v>8.9124116</v>
+      </c>
+      <c r="O43">
+        <v>3.11934406</v>
+      </c>
+      <c r="P43">
+        <v>5.793067540000001</v>
+      </c>
+      <c r="Q43">
+        <v>6.283067540000001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.3492208913670916</v>
+      </c>
+      <c r="T43">
+        <v>1.401436223113659</v>
+      </c>
+      <c r="U43">
+        <v>0.0458</v>
+      </c>
+      <c r="V43">
+        <v>0.35</v>
+      </c>
+      <c r="W43">
+        <v>0.02977</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>10.92928562802282</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2174073089297329</v>
+      </c>
+      <c r="C44">
+        <v>37.65764842260702</v>
+      </c>
+      <c r="D44">
+        <v>56.80464842260702</v>
+      </c>
+      <c r="E44">
+        <v>-8.524000000000004</v>
+      </c>
+      <c r="F44">
+        <v>20.076</v>
+      </c>
+      <c r="G44">
+        <v>0.929</v>
+      </c>
+      <c r="H44">
+        <v>19.2</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>10.3</v>
+      </c>
+      <c r="K44">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L44">
+        <v>9.81</v>
+      </c>
+      <c r="M44">
+        <v>0.9194807999999999</v>
+      </c>
+      <c r="N44">
+        <v>8.8905192</v>
+      </c>
+      <c r="O44">
+        <v>3.11168172</v>
+      </c>
+      <c r="P44">
+        <v>5.77883748</v>
+      </c>
+      <c r="Q44">
+        <v>6.26883748</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.3532826016029877</v>
+      </c>
+      <c r="T44">
+        <v>1.419773351865876</v>
+      </c>
+      <c r="U44">
+        <v>0.0458</v>
+      </c>
+      <c r="V44">
+        <v>0.35</v>
+      </c>
+      <c r="W44">
+        <v>0.02977</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>10.66906454164133</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2165685919528817</v>
+      </c>
+      <c r="C45">
+        <v>37.44765427489354</v>
+      </c>
+      <c r="D45">
+        <v>57.07265427489354</v>
+      </c>
+      <c r="E45">
+        <v>-8.046000000000003</v>
+      </c>
+      <c r="F45">
+        <v>20.554</v>
+      </c>
+      <c r="G45">
+        <v>0.929</v>
+      </c>
+      <c r="H45">
+        <v>19.2</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>10.3</v>
+      </c>
+      <c r="K45">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L45">
+        <v>9.81</v>
+      </c>
+      <c r="M45">
+        <v>0.9413731999999999</v>
+      </c>
+      <c r="N45">
+        <v>8.868626800000001</v>
+      </c>
+      <c r="O45">
+        <v>3.10401938</v>
+      </c>
+      <c r="P45">
+        <v>5.764607420000001</v>
+      </c>
+      <c r="Q45">
+        <v>6.254607420000001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.3574868279875117</v>
+      </c>
+      <c r="T45">
+        <v>1.438753888644486</v>
+      </c>
+      <c r="U45">
+        <v>0.0458</v>
+      </c>
+      <c r="V45">
+        <v>0.35</v>
+      </c>
+      <c r="W45">
+        <v>0.02977</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>10.42094676160316</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2157298749760305</v>
+      </c>
+      <c r="C46">
+        <v>37.24020103281555</v>
+      </c>
+      <c r="D46">
+        <v>57.34320103281554</v>
+      </c>
+      <c r="E46">
+        <v>-7.568000000000001</v>
+      </c>
+      <c r="F46">
+        <v>21.032</v>
+      </c>
+      <c r="G46">
+        <v>0.929</v>
+      </c>
+      <c r="H46">
+        <v>19.2</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>10.3</v>
+      </c>
+      <c r="K46">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L46">
+        <v>9.81</v>
+      </c>
+      <c r="M46">
+        <v>0.9632656000000001</v>
+      </c>
+      <c r="N46">
+        <v>8.846734400000001</v>
+      </c>
+      <c r="O46">
+        <v>3.09635704</v>
+      </c>
+      <c r="P46">
+        <v>5.750377360000001</v>
+      </c>
+      <c r="Q46">
+        <v>6.240377360000001</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.3618412053143402</v>
+      </c>
+      <c r="T46">
+        <v>1.458412301736619</v>
+      </c>
+      <c r="U46">
+        <v>0.0458</v>
+      </c>
+      <c r="V46">
+        <v>0.35</v>
+      </c>
+      <c r="W46">
+        <v>0.02977</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>10.18410706247581</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2148911579991793</v>
+      </c>
+      <c r="C47">
+        <v>37.03532500314821</v>
+      </c>
+      <c r="D47">
+        <v>57.61632500314821</v>
+      </c>
+      <c r="E47">
+        <v>-7.090000000000003</v>
+      </c>
+      <c r="F47">
+        <v>21.51</v>
+      </c>
+      <c r="G47">
+        <v>0.929</v>
+      </c>
+      <c r="H47">
+        <v>19.2</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>10.3</v>
+      </c>
+      <c r="K47">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L47">
+        <v>9.81</v>
+      </c>
+      <c r="M47">
+        <v>0.9851579999999999</v>
+      </c>
+      <c r="N47">
+        <v>8.824842</v>
+      </c>
+      <c r="O47">
+        <v>3.0886947</v>
+      </c>
+      <c r="P47">
+        <v>5.736147300000001</v>
+      </c>
+      <c r="Q47">
+        <v>6.226147300000001</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.3663539236348715</v>
+      </c>
+      <c r="T47">
+        <v>1.478785566213919</v>
+      </c>
+      <c r="U47">
+        <v>0.0458</v>
+      </c>
+      <c r="V47">
+        <v>0.35</v>
+      </c>
+      <c r="W47">
+        <v>0.02977</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>9.957793572198574</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2147102410223281</v>
+      </c>
+      <c r="C48">
+        <v>36.61658119696766</v>
+      </c>
+      <c r="D48">
+        <v>57.67558119696766</v>
+      </c>
+      <c r="E48">
+        <v>-6.612000000000002</v>
+      </c>
+      <c r="F48">
+        <v>21.988</v>
+      </c>
+      <c r="G48">
+        <v>0.929</v>
+      </c>
+      <c r="H48">
+        <v>19.2</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>10.3</v>
+      </c>
+      <c r="K48">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L48">
+        <v>9.81</v>
+      </c>
+      <c r="M48">
+        <v>1.055424</v>
+      </c>
+      <c r="N48">
+        <v>8.754576</v>
+      </c>
+      <c r="O48">
+        <v>3.0641016</v>
+      </c>
+      <c r="P48">
+        <v>5.6904744</v>
+      </c>
+      <c r="Q48">
+        <v>6.1804744</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.371033779670978</v>
+      </c>
+      <c r="T48">
+        <v>1.499913396042231</v>
+      </c>
+      <c r="U48">
+        <v>0.048</v>
+      </c>
+      <c r="V48">
+        <v>0.35</v>
+      </c>
+      <c r="W48">
+        <v>0.0312</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>9.294842641440786</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2138858240454769</v>
+      </c>
+      <c r="C49">
+        <v>36.41015502967379</v>
+      </c>
+      <c r="D49">
+        <v>57.94715502967379</v>
+      </c>
+      <c r="E49">
+        <v>-6.134</v>
+      </c>
+      <c r="F49">
+        <v>22.466</v>
+      </c>
+      <c r="G49">
+        <v>0.929</v>
+      </c>
+      <c r="H49">
+        <v>19.2</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>10.3</v>
+      </c>
+      <c r="K49">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L49">
+        <v>9.81</v>
+      </c>
+      <c r="M49">
+        <v>1.078368</v>
+      </c>
+      <c r="N49">
+        <v>8.731632000000001</v>
+      </c>
+      <c r="O49">
+        <v>3.0560712</v>
+      </c>
+      <c r="P49">
+        <v>5.675560800000001</v>
+      </c>
+      <c r="Q49">
+        <v>6.165560800000002</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.3758902340480696</v>
+      </c>
+      <c r="T49">
+        <v>1.521838502467838</v>
+      </c>
+      <c r="U49">
+        <v>0.048</v>
+      </c>
+      <c r="V49">
+        <v>0.35</v>
+      </c>
+      <c r="W49">
+        <v>0.0312</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>9.09708003204843</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2130614070686257</v>
+      </c>
+      <c r="C50">
+        <v>36.2062984511594</v>
+      </c>
+      <c r="D50">
+        <v>58.2212984511594</v>
+      </c>
+      <c r="E50">
+        <v>-5.656000000000002</v>
+      </c>
+      <c r="F50">
+        <v>22.944</v>
+      </c>
+      <c r="G50">
+        <v>0.929</v>
+      </c>
+      <c r="H50">
+        <v>19.2</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>10.3</v>
+      </c>
+      <c r="K50">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L50">
+        <v>9.81</v>
+      </c>
+      <c r="M50">
+        <v>1.101312</v>
+      </c>
+      <c r="N50">
+        <v>8.708688</v>
+      </c>
+      <c r="O50">
+        <v>3.0480408</v>
+      </c>
+      <c r="P50">
+        <v>5.660647200000001</v>
+      </c>
+      <c r="Q50">
+        <v>6.150647200000001</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.3809334751319726</v>
+      </c>
+      <c r="T50">
+        <v>1.544606882217506</v>
+      </c>
+      <c r="U50">
+        <v>0.048</v>
+      </c>
+      <c r="V50">
+        <v>0.35</v>
+      </c>
+      <c r="W50">
+        <v>0.0312</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>8.907557531380753</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2122369900917745</v>
+      </c>
+      <c r="C51">
+        <v>36.00504810434502</v>
+      </c>
+      <c r="D51">
+        <v>58.49804810434502</v>
+      </c>
+      <c r="E51">
+        <v>-5.178000000000004</v>
+      </c>
+      <c r="F51">
+        <v>23.422</v>
+      </c>
+      <c r="G51">
+        <v>0.929</v>
+      </c>
+      <c r="H51">
+        <v>19.2</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>10.3</v>
+      </c>
+      <c r="K51">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L51">
+        <v>9.81</v>
+      </c>
+      <c r="M51">
+        <v>1.124256</v>
+      </c>
+      <c r="N51">
+        <v>8.685744</v>
+      </c>
+      <c r="O51">
+        <v>3.0400104</v>
+      </c>
+      <c r="P51">
+        <v>5.6457336</v>
+      </c>
+      <c r="Q51">
+        <v>6.1357336</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.3861744903760285</v>
+      </c>
+      <c r="T51">
+        <v>1.568268139604417</v>
+      </c>
+      <c r="U51">
+        <v>0.048</v>
+      </c>
+      <c r="V51">
+        <v>0.35</v>
+      </c>
+      <c r="W51">
+        <v>0.0312</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>8.725770642985228</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2114125731149233</v>
+      </c>
+      <c r="C52">
+        <v>35.80644133219391</v>
+      </c>
+      <c r="D52">
+        <v>58.7774413321939</v>
+      </c>
+      <c r="E52">
+        <v>-4.700000000000003</v>
+      </c>
+      <c r="F52">
+        <v>23.9</v>
+      </c>
+      <c r="G52">
+        <v>0.929</v>
+      </c>
+      <c r="H52">
+        <v>19.2</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>10.3</v>
+      </c>
+      <c r="K52">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L52">
+        <v>9.81</v>
+      </c>
+      <c r="M52">
+        <v>1.1472</v>
+      </c>
+      <c r="N52">
+        <v>8.662800000000001</v>
+      </c>
+      <c r="O52">
+        <v>3.03198</v>
+      </c>
+      <c r="P52">
+        <v>5.630820000000001</v>
+      </c>
+      <c r="Q52">
+        <v>6.120820000000001</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.3916251462298467</v>
+      </c>
+      <c r="T52">
+        <v>1.592875847286803</v>
+      </c>
+      <c r="U52">
+        <v>0.048</v>
+      </c>
+      <c r="V52">
+        <v>0.35</v>
+      </c>
+      <c r="W52">
+        <v>0.0312</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>8.551255230125523</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2105881561380722</v>
+      </c>
+      <c r="C53">
+        <v>35.61051619450971</v>
+      </c>
+      <c r="D53">
+        <v>59.05951619450971</v>
+      </c>
+      <c r="E53">
+        <v>-4.222000000000001</v>
+      </c>
+      <c r="F53">
+        <v>24.378</v>
+      </c>
+      <c r="G53">
+        <v>0.929</v>
+      </c>
+      <c r="H53">
+        <v>19.2</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>10.3</v>
+      </c>
+      <c r="K53">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L53">
+        <v>9.81</v>
+      </c>
+      <c r="M53">
+        <v>1.170144</v>
+      </c>
+      <c r="N53">
+        <v>8.639856</v>
+      </c>
+      <c r="O53">
+        <v>3.0239496</v>
+      </c>
+      <c r="P53">
+        <v>5.6159064</v>
+      </c>
+      <c r="Q53">
+        <v>6.1059064</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.3972982778328004</v>
+      </c>
+      <c r="T53">
+        <v>1.618487951201124</v>
+      </c>
+      <c r="U53">
+        <v>0.048</v>
+      </c>
+      <c r="V53">
+        <v>0.35</v>
+      </c>
+      <c r="W53">
+        <v>0.0312</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>8.38358355894659</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.209763739161221</v>
+      </c>
+      <c r="C54">
+        <v>35.41731148522021</v>
+      </c>
+      <c r="D54">
+        <v>59.3443114852202</v>
+      </c>
+      <c r="E54">
+        <v>-3.744000000000003</v>
+      </c>
+      <c r="F54">
+        <v>24.856</v>
+      </c>
+      <c r="G54">
+        <v>0.929</v>
+      </c>
+      <c r="H54">
+        <v>19.2</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>10.3</v>
+      </c>
+      <c r="K54">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L54">
+        <v>9.81</v>
+      </c>
+      <c r="M54">
+        <v>1.193088</v>
+      </c>
+      <c r="N54">
+        <v>8.616912000000001</v>
+      </c>
+      <c r="O54">
+        <v>3.0159192</v>
+      </c>
+      <c r="P54">
+        <v>5.6009928</v>
+      </c>
+      <c r="Q54">
+        <v>6.0909928</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.4032077899192104</v>
+      </c>
+      <c r="T54">
+        <v>1.645167226111875</v>
+      </c>
+      <c r="U54">
+        <v>0.048</v>
+      </c>
+      <c r="V54">
+        <v>0.35</v>
+      </c>
+      <c r="W54">
+        <v>0.0312</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>8.22236079819762</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2089393221843698</v>
+      </c>
+      <c r="C55">
+        <v>35.22686675016327</v>
+      </c>
+      <c r="D55">
+        <v>59.63186675016327</v>
+      </c>
+      <c r="E55">
+        <v>-3.266000000000002</v>
+      </c>
+      <c r="F55">
+        <v>25.334</v>
+      </c>
+      <c r="G55">
+        <v>0.929</v>
+      </c>
+      <c r="H55">
+        <v>19.2</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>10.3</v>
+      </c>
+      <c r="K55">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L55">
+        <v>9.81</v>
+      </c>
+      <c r="M55">
+        <v>1.216032</v>
+      </c>
+      <c r="N55">
+        <v>8.593968</v>
+      </c>
+      <c r="O55">
+        <v>3.0078888</v>
+      </c>
+      <c r="P55">
+        <v>5.5860792</v>
+      </c>
+      <c r="Q55">
+        <v>6.076079200000001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.4093687706050421</v>
+      </c>
+      <c r="T55">
+        <v>1.672981789316701</v>
+      </c>
+      <c r="U55">
+        <v>0.048</v>
+      </c>
+      <c r="V55">
+        <v>0.35</v>
+      </c>
+      <c r="W55">
+        <v>0.0312</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>8.067221915212759</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2081149052075186</v>
+      </c>
+      <c r="C56">
+        <v>35.0392223053928</v>
+      </c>
+      <c r="D56">
+        <v>59.92222230539279</v>
+      </c>
+      <c r="E56">
+        <v>-2.788</v>
+      </c>
+      <c r="F56">
+        <v>25.812</v>
+      </c>
+      <c r="G56">
+        <v>0.929</v>
+      </c>
+      <c r="H56">
+        <v>19.2</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>10.3</v>
+      </c>
+      <c r="K56">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L56">
+        <v>9.81</v>
+      </c>
+      <c r="M56">
+        <v>1.238976</v>
+      </c>
+      <c r="N56">
+        <v>8.571024000000001</v>
+      </c>
+      <c r="O56">
+        <v>2.9998584</v>
+      </c>
+      <c r="P56">
+        <v>5.5711656</v>
+      </c>
+      <c r="Q56">
+        <v>6.061165600000001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.4157976200163448</v>
+      </c>
+      <c r="T56">
+        <v>1.702005681356519</v>
+      </c>
+      <c r="U56">
+        <v>0.048</v>
+      </c>
+      <c r="V56">
+        <v>0.35</v>
+      </c>
+      <c r="W56">
+        <v>0.0312</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>7.917828916782892</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2072904882306674</v>
+      </c>
+      <c r="C57">
+        <v>34.85441925602175</v>
+      </c>
+      <c r="D57">
+        <v>60.21541925602175</v>
+      </c>
+      <c r="E57">
+        <v>-2.310000000000002</v>
+      </c>
+      <c r="F57">
+        <v>26.29</v>
+      </c>
+      <c r="G57">
+        <v>0.929</v>
+      </c>
+      <c r="H57">
+        <v>19.2</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>10.3</v>
+      </c>
+      <c r="K57">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L57">
+        <v>9.81</v>
+      </c>
+      <c r="M57">
+        <v>1.26192</v>
+      </c>
+      <c r="N57">
+        <v>8.548080000000001</v>
+      </c>
+      <c r="O57">
+        <v>2.991828</v>
+      </c>
+      <c r="P57">
+        <v>5.556252000000001</v>
+      </c>
+      <c r="Q57">
+        <v>6.046252000000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.4225121960681498</v>
+      </c>
+      <c r="T57">
+        <v>1.732319524153662</v>
+      </c>
+      <c r="U57">
+        <v>0.048</v>
+      </c>
+      <c r="V57">
+        <v>0.35</v>
+      </c>
+      <c r="W57">
+        <v>0.0312</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>7.773868391023203</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2070120712538162</v>
+      </c>
+      <c r="C58">
+        <v>34.47608508181015</v>
+      </c>
+      <c r="D58">
+        <v>60.31508508181015</v>
+      </c>
+      <c r="E58">
+        <v>-1.832000000000001</v>
+      </c>
+      <c r="F58">
+        <v>26.768</v>
+      </c>
+      <c r="G58">
+        <v>0.929</v>
+      </c>
+      <c r="H58">
+        <v>19.2</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>10.3</v>
+      </c>
+      <c r="K58">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L58">
+        <v>9.81</v>
+      </c>
+      <c r="M58">
+        <v>1.325016</v>
+      </c>
+      <c r="N58">
+        <v>8.484984000000001</v>
+      </c>
+      <c r="O58">
+        <v>2.9697444</v>
+      </c>
+      <c r="P58">
+        <v>5.515239600000001</v>
+      </c>
+      <c r="Q58">
+        <v>6.005239600000001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.4295319801223096</v>
+      </c>
+      <c r="T58">
+        <v>1.764011268896129</v>
+      </c>
+      <c r="U58">
+        <v>0.0495</v>
+      </c>
+      <c r="V58">
+        <v>0.35</v>
+      </c>
+      <c r="W58">
+        <v>0.032175</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>7.40368418192686</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.206197404276965</v>
+      </c>
+      <c r="C59">
+        <v>34.29161835512676</v>
+      </c>
+      <c r="D59">
+        <v>60.60861835512676</v>
+      </c>
+      <c r="E59">
+        <v>-1.353999999999999</v>
+      </c>
+      <c r="F59">
+        <v>27.246</v>
+      </c>
+      <c r="G59">
+        <v>0.929</v>
+      </c>
+      <c r="H59">
+        <v>19.2</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>10.3</v>
+      </c>
+      <c r="K59">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L59">
+        <v>9.81</v>
+      </c>
+      <c r="M59">
+        <v>1.348677</v>
+      </c>
+      <c r="N59">
+        <v>8.461323</v>
+      </c>
+      <c r="O59">
+        <v>2.96146305</v>
+      </c>
+      <c r="P59">
+        <v>5.49985995</v>
+      </c>
+      <c r="Q59">
+        <v>5.98985995</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.4368782657603838</v>
+      </c>
+      <c r="T59">
+        <v>1.797177048277782</v>
+      </c>
+      <c r="U59">
+        <v>0.0495</v>
+      </c>
+      <c r="V59">
+        <v>0.35</v>
+      </c>
+      <c r="W59">
+        <v>0.032175</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>7.273794985752704</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2053827373001139</v>
+      </c>
+      <c r="C60">
+        <v>34.11002265659734</v>
+      </c>
+      <c r="D60">
+        <v>60.90502265659733</v>
+      </c>
+      <c r="E60">
+        <v>-0.8760000000000048</v>
+      </c>
+      <c r="F60">
+        <v>27.724</v>
+      </c>
+      <c r="G60">
+        <v>0.929</v>
+      </c>
+      <c r="H60">
+        <v>19.2</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>10.3</v>
+      </c>
+      <c r="K60">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L60">
+        <v>9.81</v>
+      </c>
+      <c r="M60">
+        <v>1.372338</v>
+      </c>
+      <c r="N60">
+        <v>8.437662000000001</v>
+      </c>
+      <c r="O60">
+        <v>2.9531817</v>
+      </c>
+      <c r="P60">
+        <v>5.484480300000001</v>
+      </c>
+      <c r="Q60">
+        <v>5.974480300000002</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.4445743745240806</v>
+      </c>
+      <c r="T60">
+        <v>1.831922150487132</v>
+      </c>
+      <c r="U60">
+        <v>0.0495</v>
+      </c>
+      <c r="V60">
+        <v>0.35</v>
+      </c>
+      <c r="W60">
+        <v>0.032175</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>7.14838472737766</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2045680703232626</v>
+      </c>
+      <c r="C61">
+        <v>33.93134031521488</v>
+      </c>
+      <c r="D61">
+        <v>61.20434031521487</v>
+      </c>
+      <c r="E61">
+        <v>-0.3980000000000032</v>
+      </c>
+      <c r="F61">
+        <v>28.202</v>
+      </c>
+      <c r="G61">
+        <v>0.929</v>
+      </c>
+      <c r="H61">
+        <v>19.2</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>10.3</v>
+      </c>
+      <c r="K61">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L61">
+        <v>9.81</v>
+      </c>
+      <c r="M61">
+        <v>1.395999</v>
+      </c>
+      <c r="N61">
+        <v>8.414001000000001</v>
+      </c>
+      <c r="O61">
+        <v>2.94490035</v>
+      </c>
+      <c r="P61">
+        <v>5.469100650000001</v>
+      </c>
+      <c r="Q61">
+        <v>5.959100650000001</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.4526459032274698</v>
+      </c>
+      <c r="T61">
+        <v>1.868362135731084</v>
+      </c>
+      <c r="U61">
+        <v>0.0495</v>
+      </c>
+      <c r="V61">
+        <v>0.35</v>
+      </c>
+      <c r="W61">
+        <v>0.032175</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>7.027225664201766</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2037534033464114</v>
+      </c>
+      <c r="C62">
+        <v>33.75561449618499</v>
+      </c>
+      <c r="D62">
+        <v>61.50661449618498</v>
+      </c>
+      <c r="E62">
+        <v>0.07999999999999474</v>
+      </c>
+      <c r="F62">
+        <v>28.68</v>
+      </c>
+      <c r="G62">
+        <v>0.929</v>
+      </c>
+      <c r="H62">
+        <v>19.2</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>10.3</v>
+      </c>
+      <c r="K62">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L62">
+        <v>9.81</v>
+      </c>
+      <c r="M62">
+        <v>1.41966</v>
+      </c>
+      <c r="N62">
+        <v>8.39034</v>
+      </c>
+      <c r="O62">
+        <v>2.936619</v>
+      </c>
+      <c r="P62">
+        <v>5.453721</v>
+      </c>
+      <c r="Q62">
+        <v>5.943721</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.4611210083660286</v>
+      </c>
+      <c r="T62">
+        <v>1.906624120237234</v>
+      </c>
+      <c r="U62">
+        <v>0.0495</v>
+      </c>
+      <c r="V62">
+        <v>0.35</v>
+      </c>
+      <c r="W62">
+        <v>0.032175</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>6.910105236465069</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2029387363695603</v>
+      </c>
+      <c r="C63">
+        <v>33.58288922167782</v>
+      </c>
+      <c r="D63">
+        <v>61.81188922167782</v>
+      </c>
+      <c r="E63">
+        <v>0.5579999999999963</v>
+      </c>
+      <c r="F63">
+        <v>29.158</v>
+      </c>
+      <c r="G63">
+        <v>0.929</v>
+      </c>
+      <c r="H63">
+        <v>19.2</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>10.3</v>
+      </c>
+      <c r="K63">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L63">
+        <v>9.81</v>
+      </c>
+      <c r="M63">
+        <v>1.443321</v>
+      </c>
+      <c r="N63">
+        <v>8.366679000000001</v>
+      </c>
+      <c r="O63">
+        <v>2.92833765</v>
+      </c>
+      <c r="P63">
+        <v>5.438341350000001</v>
+      </c>
+      <c r="Q63">
+        <v>5.928341350000001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.4700307342809237</v>
+      </c>
+      <c r="T63">
+        <v>1.946848257794982</v>
+      </c>
+      <c r="U63">
+        <v>0.0495</v>
+      </c>
+      <c r="V63">
+        <v>0.35</v>
+      </c>
+      <c r="W63">
+        <v>0.032175</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>6.796824822752528</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2021240693927091</v>
+      </c>
+      <c r="C64">
+        <v>33.4132093922009</v>
+      </c>
+      <c r="D64">
+        <v>62.12020939220089</v>
+      </c>
+      <c r="E64">
+        <v>1.035999999999998</v>
+      </c>
+      <c r="F64">
+        <v>29.636</v>
+      </c>
+      <c r="G64">
+        <v>0.929</v>
+      </c>
+      <c r="H64">
+        <v>19.2</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>10.3</v>
+      </c>
+      <c r="K64">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L64">
+        <v>9.81</v>
+      </c>
+      <c r="M64">
+        <v>1.466982</v>
+      </c>
+      <c r="N64">
+        <v>8.343018000000001</v>
+      </c>
+      <c r="O64">
+        <v>2.9200563</v>
+      </c>
+      <c r="P64">
+        <v>5.4229617</v>
+      </c>
+      <c r="Q64">
+        <v>5.9129617</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.4794093931387081</v>
+      </c>
+      <c r="T64">
+        <v>1.98918945522419</v>
+      </c>
+      <c r="U64">
+        <v>0.0495</v>
+      </c>
+      <c r="V64">
+        <v>0.35</v>
+      </c>
+      <c r="W64">
+        <v>0.032175</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>6.687198615933938</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2013094024158578</v>
+      </c>
+      <c r="C65">
+        <v>33.24662080861486</v>
+      </c>
+      <c r="D65">
+        <v>62.43162080861486</v>
+      </c>
+      <c r="E65">
+        <v>1.513999999999996</v>
+      </c>
+      <c r="F65">
+        <v>30.114</v>
+      </c>
+      <c r="G65">
+        <v>0.929</v>
+      </c>
+      <c r="H65">
+        <v>19.2</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>10.3</v>
+      </c>
+      <c r="K65">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L65">
+        <v>9.81</v>
+      </c>
+      <c r="M65">
+        <v>1.490643</v>
+      </c>
+      <c r="N65">
+        <v>8.319357</v>
+      </c>
+      <c r="O65">
+        <v>2.91177495</v>
+      </c>
+      <c r="P65">
+        <v>5.40758205</v>
+      </c>
+      <c r="Q65">
+        <v>5.89758205</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.4892950065293456</v>
+      </c>
+      <c r="T65">
+        <v>2.03381936602795</v>
+      </c>
+      <c r="U65">
+        <v>0.0495</v>
+      </c>
+      <c r="V65">
+        <v>0.35</v>
+      </c>
+      <c r="W65">
+        <v>0.032175</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>6.581052606157209</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2004947354390067</v>
+      </c>
+      <c r="C66">
+        <v>33.08317019481464</v>
+      </c>
+      <c r="D66">
+        <v>62.74617019481464</v>
+      </c>
+      <c r="E66">
+        <v>1.991999999999997</v>
+      </c>
+      <c r="F66">
+        <v>30.592</v>
+      </c>
+      <c r="G66">
+        <v>0.929</v>
+      </c>
+      <c r="H66">
+        <v>19.2</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>10.3</v>
+      </c>
+      <c r="K66">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L66">
+        <v>9.81</v>
+      </c>
+      <c r="M66">
+        <v>1.514304</v>
+      </c>
+      <c r="N66">
+        <v>8.295696</v>
+      </c>
+      <c r="O66">
+        <v>2.9034936</v>
+      </c>
+      <c r="P66">
+        <v>5.3922024</v>
+      </c>
+      <c r="Q66">
+        <v>5.882202400000001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.4997298206639075</v>
+      </c>
+      <c r="T66">
+        <v>2.080928716320807</v>
+      </c>
+      <c r="U66">
+        <v>0.0495</v>
+      </c>
+      <c r="V66">
+        <v>0.35</v>
+      </c>
+      <c r="W66">
+        <v>0.032175</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>6.478223659186002</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1996800684621555</v>
+      </c>
+      <c r="C67">
+        <v>32.9229052210999</v>
+      </c>
+      <c r="D67">
+        <v>63.0639052210999</v>
+      </c>
+      <c r="E67">
+        <v>2.469999999999999</v>
+      </c>
+      <c r="F67">
+        <v>31.07</v>
+      </c>
+      <c r="G67">
+        <v>0.929</v>
+      </c>
+      <c r="H67">
+        <v>19.2</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>10.3</v>
+      </c>
+      <c r="K67">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L67">
+        <v>9.81</v>
+      </c>
+      <c r="M67">
+        <v>1.537965</v>
+      </c>
+      <c r="N67">
+        <v>8.272035000000001</v>
+      </c>
+      <c r="O67">
+        <v>2.89521225</v>
+      </c>
+      <c r="P67">
+        <v>5.376822750000001</v>
+      </c>
+      <c r="Q67">
+        <v>5.866822750000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.5107609098918728</v>
+      </c>
+      <c r="T67">
+        <v>2.130730029487542</v>
+      </c>
+      <c r="U67">
+        <v>0.0495</v>
+      </c>
+      <c r="V67">
+        <v>0.35</v>
+      </c>
+      <c r="W67">
+        <v>0.032175</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>6.37855867981391</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1988654014853042</v>
+      </c>
+      <c r="C68">
+        <v>32.76587452825916</v>
+      </c>
+      <c r="D68">
+        <v>63.38487452825916</v>
+      </c>
+      <c r="E68">
+        <v>2.947999999999997</v>
+      </c>
+      <c r="F68">
+        <v>31.548</v>
+      </c>
+      <c r="G68">
+        <v>0.929</v>
+      </c>
+      <c r="H68">
+        <v>19.2</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>10.3</v>
+      </c>
+      <c r="K68">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L68">
+        <v>9.81</v>
+      </c>
+      <c r="M68">
+        <v>1.561626</v>
+      </c>
+      <c r="N68">
+        <v>8.248374</v>
+      </c>
+      <c r="O68">
+        <v>2.8869309</v>
+      </c>
+      <c r="P68">
+        <v>5.361443100000001</v>
+      </c>
+      <c r="Q68">
+        <v>5.851443100000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.5224408867214831</v>
+      </c>
+      <c r="T68">
+        <v>2.183460831664085</v>
+      </c>
+      <c r="U68">
+        <v>0.0495</v>
+      </c>
+      <c r="V68">
+        <v>0.35</v>
+      </c>
+      <c r="W68">
+        <v>0.032175</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>6.281913851331881</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1980507345084531</v>
+      </c>
+      <c r="C69">
+        <v>32.61212775239284</v>
+      </c>
+      <c r="D69">
+        <v>63.70912775239285</v>
+      </c>
+      <c r="E69">
+        <v>3.426000000000002</v>
+      </c>
+      <c r="F69">
+        <v>32.026</v>
+      </c>
+      <c r="G69">
+        <v>0.929</v>
+      </c>
+      <c r="H69">
+        <v>19.2</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>10.3</v>
+      </c>
+      <c r="K69">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L69">
+        <v>9.81</v>
+      </c>
+      <c r="M69">
+        <v>1.585287</v>
+      </c>
+      <c r="N69">
+        <v>8.224712999999999</v>
+      </c>
+      <c r="O69">
+        <v>2.87864955</v>
+      </c>
+      <c r="P69">
+        <v>5.34606345</v>
+      </c>
+      <c r="Q69">
+        <v>5.83606345</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.5348287409347066</v>
+      </c>
+      <c r="T69">
+        <v>2.239387440033147</v>
+      </c>
+      <c r="U69">
+        <v>0.0495</v>
+      </c>
+      <c r="V69">
+        <v>0.35</v>
+      </c>
+      <c r="W69">
+        <v>0.032175</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>6.188153943103045</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.197854867531602</v>
+      </c>
+      <c r="C70">
+        <v>32.21258190123054</v>
+      </c>
+      <c r="D70">
+        <v>63.78758190123055</v>
+      </c>
+      <c r="E70">
+        <v>3.903999999999996</v>
+      </c>
+      <c r="F70">
+        <v>32.504</v>
+      </c>
+      <c r="G70">
+        <v>0.929</v>
+      </c>
+      <c r="H70">
+        <v>19.2</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>10.3</v>
+      </c>
+      <c r="K70">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L70">
+        <v>9.81</v>
+      </c>
+      <c r="M70">
+        <v>1.6544536</v>
+      </c>
+      <c r="N70">
+        <v>8.1555464</v>
+      </c>
+      <c r="O70">
+        <v>2.85444124</v>
+      </c>
+      <c r="P70">
+        <v>5.301105160000001</v>
+      </c>
+      <c r="Q70">
+        <v>5.791105160000001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.5479908360362562</v>
+      </c>
+      <c r="T70">
+        <v>2.298809461425273</v>
+      </c>
+      <c r="U70">
+        <v>0.0509</v>
+      </c>
+      <c r="V70">
+        <v>0.35</v>
+      </c>
+      <c r="W70">
+        <v>0.033085</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>5.929450061337472</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1970493005547508</v>
+      </c>
+      <c r="C71">
+        <v>32.05929214849668</v>
+      </c>
+      <c r="D71">
+        <v>64.11229214849668</v>
+      </c>
+      <c r="E71">
+        <v>4.381999999999998</v>
+      </c>
+      <c r="F71">
+        <v>32.982</v>
+      </c>
+      <c r="G71">
+        <v>0.929</v>
+      </c>
+      <c r="H71">
+        <v>19.2</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>10.3</v>
+      </c>
+      <c r="K71">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L71">
+        <v>9.81</v>
+      </c>
+      <c r="M71">
+        <v>1.6787838</v>
+      </c>
+      <c r="N71">
+        <v>8.131216200000001</v>
+      </c>
+      <c r="O71">
+        <v>2.84592567</v>
+      </c>
+      <c r="P71">
+        <v>5.285290530000001</v>
+      </c>
+      <c r="Q71">
+        <v>5.775290530000001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.5620020985637122</v>
+      </c>
+      <c r="T71">
+        <v>2.362065161616893</v>
+      </c>
+      <c r="U71">
+        <v>0.0509</v>
+      </c>
+      <c r="V71">
+        <v>0.35</v>
+      </c>
+      <c r="W71">
+        <v>0.033085</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>5.843516002477508</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1962437335778995</v>
+      </c>
+      <c r="C72">
+        <v>31.90932518094196</v>
+      </c>
+      <c r="D72">
+        <v>64.44032518094195</v>
+      </c>
+      <c r="E72">
+        <v>4.859999999999999</v>
+      </c>
+      <c r="F72">
+        <v>33.46</v>
+      </c>
+      <c r="G72">
+        <v>0.929</v>
+      </c>
+      <c r="H72">
+        <v>19.2</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>10.3</v>
+      </c>
+      <c r="K72">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L72">
+        <v>9.81</v>
+      </c>
+      <c r="M72">
+        <v>1.703114</v>
+      </c>
+      <c r="N72">
+        <v>8.106886000000001</v>
+      </c>
+      <c r="O72">
+        <v>2.8374101</v>
+      </c>
+      <c r="P72">
+        <v>5.269475900000002</v>
+      </c>
+      <c r="Q72">
+        <v>5.759475900000002</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.5769474452596652</v>
+      </c>
+      <c r="T72">
+        <v>2.429537908487953</v>
+      </c>
+      <c r="U72">
+        <v>0.0509</v>
+      </c>
+      <c r="V72">
+        <v>0.35</v>
+      </c>
+      <c r="W72">
+        <v>0.033085</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>5.760037202442115</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1954381666010484</v>
+      </c>
+      <c r="C73">
+        <v>31.76273226434798</v>
+      </c>
+      <c r="D73">
+        <v>64.77173226434797</v>
+      </c>
+      <c r="E73">
+        <v>5.337999999999994</v>
+      </c>
+      <c r="F73">
+        <v>33.938</v>
+      </c>
+      <c r="G73">
+        <v>0.929</v>
+      </c>
+      <c r="H73">
+        <v>19.2</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>10.3</v>
+      </c>
+      <c r="K73">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L73">
+        <v>9.81</v>
+      </c>
+      <c r="M73">
+        <v>1.7274442</v>
+      </c>
+      <c r="N73">
+        <v>8.082555800000002</v>
+      </c>
+      <c r="O73">
+        <v>2.82889453</v>
+      </c>
+      <c r="P73">
+        <v>5.253661270000001</v>
+      </c>
+      <c r="Q73">
+        <v>5.743661270000001</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.5929235055208564</v>
+      </c>
+      <c r="T73">
+        <v>2.501663948246672</v>
+      </c>
+      <c r="U73">
+        <v>0.0509</v>
+      </c>
+      <c r="V73">
+        <v>0.35</v>
+      </c>
+      <c r="W73">
+        <v>0.033085</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>5.678909917900678</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1946325996241972</v>
+      </c>
+      <c r="C74">
+        <v>31.61956572455745</v>
+      </c>
+      <c r="D74">
+        <v>65.10656572455744</v>
+      </c>
+      <c r="E74">
+        <v>5.815999999999995</v>
+      </c>
+      <c r="F74">
+        <v>34.416</v>
+      </c>
+      <c r="G74">
+        <v>0.929</v>
+      </c>
+      <c r="H74">
+        <v>19.2</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>10.3</v>
+      </c>
+      <c r="K74">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L74">
+        <v>9.81</v>
+      </c>
+      <c r="M74">
+        <v>1.7517744</v>
+      </c>
+      <c r="N74">
+        <v>8.0582256</v>
+      </c>
+      <c r="O74">
+        <v>2.82037896</v>
+      </c>
+      <c r="P74">
+        <v>5.237846640000001</v>
+      </c>
+      <c r="Q74">
+        <v>5.727846640000001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.6100407129435612</v>
+      </c>
+      <c r="T74">
+        <v>2.578941847988157</v>
+      </c>
+      <c r="U74">
+        <v>0.0509</v>
+      </c>
+      <c r="V74">
+        <v>0.35</v>
+      </c>
+      <c r="W74">
+        <v>0.033085</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>5.600036169040945</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.193827032647346</v>
+      </c>
+      <c r="C75">
+        <v>31.47987897501614</v>
+      </c>
+      <c r="D75">
+        <v>65.44487897501614</v>
+      </c>
+      <c r="E75">
+        <v>6.293999999999997</v>
+      </c>
+      <c r="F75">
+        <v>34.894</v>
+      </c>
+      <c r="G75">
+        <v>0.929</v>
+      </c>
+      <c r="H75">
+        <v>19.2</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>10.3</v>
+      </c>
+      <c r="K75">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L75">
+        <v>9.81</v>
+      </c>
+      <c r="M75">
+        <v>1.7761046</v>
+      </c>
+      <c r="N75">
+        <v>8.0338954</v>
+      </c>
+      <c r="O75">
+        <v>2.81186339</v>
+      </c>
+      <c r="P75">
+        <v>5.22203201</v>
+      </c>
+      <c r="Q75">
+        <v>5.712032010000001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.628425861656837</v>
+      </c>
+      <c r="T75">
+        <v>2.661944036599383</v>
+      </c>
+      <c r="U75">
+        <v>0.0509</v>
+      </c>
+      <c r="V75">
+        <v>0.35</v>
+      </c>
+      <c r="W75">
+        <v>0.033085</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>5.523323344807507</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1930214656704948</v>
+      </c>
+      <c r="C76">
+        <v>31.34372654517826</v>
+      </c>
+      <c r="D76">
+        <v>65.78672654517825</v>
+      </c>
+      <c r="E76">
+        <v>6.771999999999998</v>
+      </c>
+      <c r="F76">
+        <v>35.372</v>
+      </c>
+      <c r="G76">
+        <v>0.929</v>
+      </c>
+      <c r="H76">
+        <v>19.2</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>10.3</v>
+      </c>
+      <c r="K76">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L76">
+        <v>9.81</v>
+      </c>
+      <c r="M76">
+        <v>1.8004348</v>
+      </c>
+      <c r="N76">
+        <v>8.009565200000001</v>
+      </c>
+      <c r="O76">
+        <v>2.80334782</v>
+      </c>
+      <c r="P76">
+        <v>5.206217380000001</v>
+      </c>
+      <c r="Q76">
+        <v>5.696217380000001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.6482252525788261</v>
+      </c>
+      <c r="T76">
+        <v>2.751331008949933</v>
+      </c>
+      <c r="U76">
+        <v>0.0509</v>
+      </c>
+      <c r="V76">
+        <v>0.35</v>
+      </c>
+      <c r="W76">
+        <v>0.033085</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>5.448683840147947</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1922158986936436</v>
+      </c>
+      <c r="C77">
+        <v>31.21116410980618</v>
+      </c>
+      <c r="D77">
+        <v>66.13216410980617</v>
+      </c>
+      <c r="E77">
+        <v>7.249999999999993</v>
+      </c>
+      <c r="F77">
+        <v>35.84999999999999</v>
+      </c>
+      <c r="G77">
+        <v>0.929</v>
+      </c>
+      <c r="H77">
+        <v>19.2</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>10.3</v>
+      </c>
+      <c r="K77">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L77">
+        <v>9.81</v>
+      </c>
+      <c r="M77">
+        <v>1.824765</v>
+      </c>
+      <c r="N77">
+        <v>7.985235000000001</v>
+      </c>
+      <c r="O77">
+        <v>2.79483225</v>
+      </c>
+      <c r="P77">
+        <v>5.190402750000001</v>
+      </c>
+      <c r="Q77">
+        <v>5.680402750000001</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.6696085947745745</v>
+      </c>
+      <c r="T77">
+        <v>2.847868939088527</v>
+      </c>
+      <c r="U77">
+        <v>0.0509</v>
+      </c>
+      <c r="V77">
+        <v>0.35</v>
+      </c>
+      <c r="W77">
+        <v>0.033085</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>5.376034722279308</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1914103317167924</v>
+      </c>
+      <c r="C78">
+        <v>31.08224851919875</v>
+      </c>
+      <c r="D78">
+        <v>66.48124851919874</v>
+      </c>
+      <c r="E78">
+        <v>7.727999999999994</v>
+      </c>
+      <c r="F78">
+        <v>36.328</v>
+      </c>
+      <c r="G78">
+        <v>0.929</v>
+      </c>
+      <c r="H78">
+        <v>19.2</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>10.3</v>
+      </c>
+      <c r="K78">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L78">
+        <v>9.81</v>
+      </c>
+      <c r="M78">
+        <v>1.8490952</v>
+      </c>
+      <c r="N78">
+        <v>7.960904800000001</v>
+      </c>
+      <c r="O78">
+        <v>2.78631668</v>
+      </c>
+      <c r="P78">
+        <v>5.174588120000001</v>
+      </c>
+      <c r="Q78">
+        <v>5.664588120000001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.6927738821533018</v>
+      </c>
+      <c r="T78">
+        <v>2.952451696738671</v>
+      </c>
+      <c r="U78">
+        <v>0.0509</v>
+      </c>
+      <c r="V78">
+        <v>0.35</v>
+      </c>
+      <c r="W78">
+        <v>0.033085</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>5.305297423301949</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1906047647399412</v>
+      </c>
+      <c r="C79">
+        <v>30.95703783038179</v>
+      </c>
+      <c r="D79">
+        <v>66.83403783038179</v>
+      </c>
+      <c r="E79">
+        <v>8.205999999999996</v>
+      </c>
+      <c r="F79">
+        <v>36.806</v>
+      </c>
+      <c r="G79">
+        <v>0.929</v>
+      </c>
+      <c r="H79">
+        <v>19.2</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>10.3</v>
+      </c>
+      <c r="K79">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L79">
+        <v>9.81</v>
+      </c>
+      <c r="M79">
+        <v>1.8734254</v>
+      </c>
+      <c r="N79">
+        <v>7.9365746</v>
+      </c>
+      <c r="O79">
+        <v>2.77780111</v>
+      </c>
+      <c r="P79">
+        <v>5.15877349</v>
+      </c>
+      <c r="Q79">
+        <v>5.64877349</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.7179535423475705</v>
+      </c>
+      <c r="T79">
+        <v>3.066128607227958</v>
+      </c>
+      <c r="U79">
+        <v>0.0509</v>
+      </c>
+      <c r="V79">
+        <v>0.35</v>
+      </c>
+      <c r="W79">
+        <v>0.033085</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>5.236397456765559</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.18979919776309</v>
+      </c>
+      <c r="C80">
+        <v>30.83559133929678</v>
+      </c>
+      <c r="D80">
+        <v>67.19059133929677</v>
+      </c>
+      <c r="E80">
+        <v>8.683999999999997</v>
+      </c>
+      <c r="F80">
+        <v>37.284</v>
+      </c>
+      <c r="G80">
+        <v>0.929</v>
+      </c>
+      <c r="H80">
+        <v>19.2</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>10.3</v>
+      </c>
+      <c r="K80">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L80">
+        <v>9.81</v>
+      </c>
+      <c r="M80">
+        <v>1.8977556</v>
+      </c>
+      <c r="N80">
+        <v>7.912244400000001</v>
+      </c>
+      <c r="O80">
+        <v>2.76928554</v>
+      </c>
+      <c r="P80">
+        <v>5.14295886</v>
+      </c>
+      <c r="Q80">
+        <v>5.63295886</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.7454222625595002</v>
+      </c>
+      <c r="T80">
+        <v>3.190139782307179</v>
+      </c>
+      <c r="U80">
+        <v>0.0509</v>
+      </c>
+      <c r="V80">
+        <v>0.35</v>
+      </c>
+      <c r="W80">
+        <v>0.033085</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>5.169264156037796</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1889936307862388</v>
+      </c>
+      <c r="C81">
+        <v>30.71796961402585</v>
+      </c>
+      <c r="D81">
+        <v>67.55096961402585</v>
+      </c>
+      <c r="E81">
+        <v>9.161999999999999</v>
+      </c>
+      <c r="F81">
+        <v>37.762</v>
+      </c>
+      <c r="G81">
+        <v>0.929</v>
+      </c>
+      <c r="H81">
+        <v>19.2</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>10.3</v>
+      </c>
+      <c r="K81">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L81">
+        <v>9.81</v>
+      </c>
+      <c r="M81">
+        <v>1.9220858</v>
+      </c>
+      <c r="N81">
+        <v>7.887914200000001</v>
+      </c>
+      <c r="O81">
+        <v>2.76076997</v>
+      </c>
+      <c r="P81">
+        <v>5.127144230000001</v>
+      </c>
+      <c r="Q81">
+        <v>5.617144230000001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.7755070513630422</v>
+      </c>
+      <c r="T81">
+        <v>3.325961545489184</v>
+      </c>
+      <c r="U81">
+        <v>0.0509</v>
+      </c>
+      <c r="V81">
+        <v>0.35</v>
+      </c>
+      <c r="W81">
+        <v>0.033085</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>5.103830432543647</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1881880638093876</v>
+      </c>
+      <c r="C82">
+        <v>30.60423452909144</v>
+      </c>
+      <c r="D82">
+        <v>67.91523452909144</v>
+      </c>
+      <c r="E82">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="F82">
+        <v>38.24</v>
+      </c>
+      <c r="G82">
+        <v>0.929</v>
+      </c>
+      <c r="H82">
+        <v>19.2</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>10.3</v>
+      </c>
+      <c r="K82">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L82">
+        <v>9.81</v>
+      </c>
+      <c r="M82">
+        <v>1.946416</v>
+      </c>
+      <c r="N82">
+        <v>7.863584</v>
+      </c>
+      <c r="O82">
+        <v>2.7522544</v>
+      </c>
+      <c r="P82">
+        <v>5.1113296</v>
+      </c>
+      <c r="Q82">
+        <v>5.601329600000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.8086003190469384</v>
+      </c>
+      <c r="T82">
+        <v>3.47536548498939</v>
+      </c>
+      <c r="U82">
+        <v>0.0509</v>
+      </c>
+      <c r="V82">
+        <v>0.35</v>
+      </c>
+      <c r="W82">
+        <v>0.033085</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>5.04003255213685</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1873824968325365</v>
+      </c>
+      <c r="C83">
+        <v>30.49444930087172</v>
+      </c>
+      <c r="D83">
+        <v>68.28344930087172</v>
+      </c>
+      <c r="E83">
+        <v>10.118</v>
+      </c>
+      <c r="F83">
+        <v>38.718</v>
+      </c>
+      <c r="G83">
+        <v>0.929</v>
+      </c>
+      <c r="H83">
+        <v>19.2</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>10.3</v>
+      </c>
+      <c r="K83">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L83">
+        <v>9.81</v>
+      </c>
+      <c r="M83">
+        <v>1.9707462</v>
+      </c>
+      <c r="N83">
+        <v>7.8392538</v>
+      </c>
+      <c r="O83">
+        <v>2.74373883</v>
+      </c>
+      <c r="P83">
+        <v>5.09551497</v>
+      </c>
+      <c r="Q83">
+        <v>5.58551497</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.8451770885922973</v>
+      </c>
+      <c r="T83">
+        <v>3.640496154963301</v>
+      </c>
+      <c r="U83">
+        <v>0.0509</v>
+      </c>
+      <c r="V83">
+        <v>0.35</v>
+      </c>
+      <c r="W83">
+        <v>0.033085</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>4.977809928036395</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1865769298556852</v>
+      </c>
+      <c r="C84">
+        <v>30.38867852417468</v>
+      </c>
+      <c r="D84">
+        <v>68.65567852417468</v>
+      </c>
+      <c r="E84">
+        <v>10.596</v>
+      </c>
+      <c r="F84">
+        <v>39.196</v>
+      </c>
+      <c r="G84">
+        <v>0.929</v>
+      </c>
+      <c r="H84">
+        <v>19.2</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>10.3</v>
+      </c>
+      <c r="K84">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L84">
+        <v>9.81</v>
+      </c>
+      <c r="M84">
+        <v>1.9950764</v>
+      </c>
+      <c r="N84">
+        <v>7.8149236</v>
+      </c>
+      <c r="O84">
+        <v>2.73522326</v>
+      </c>
+      <c r="P84">
+        <v>5.07970034</v>
+      </c>
+      <c r="Q84">
+        <v>5.569700340000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.8858179436426961</v>
+      </c>
+      <c r="T84">
+        <v>3.823974677156535</v>
+      </c>
+      <c r="U84">
+        <v>0.0509</v>
+      </c>
+      <c r="V84">
+        <v>0.35</v>
+      </c>
+      <c r="W84">
+        <v>0.033085</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>4.917104928914001</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1857713628788341</v>
+      </c>
+      <c r="C85">
+        <v>30.28698821001449</v>
+      </c>
+      <c r="D85">
+        <v>69.03198821001449</v>
+      </c>
+      <c r="E85">
+        <v>11.074</v>
+      </c>
+      <c r="F85">
+        <v>39.674</v>
+      </c>
+      <c r="G85">
+        <v>0.929</v>
+      </c>
+      <c r="H85">
+        <v>19.2</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>10.3</v>
+      </c>
+      <c r="K85">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L85">
+        <v>9.81</v>
+      </c>
+      <c r="M85">
+        <v>2.0194066</v>
+      </c>
+      <c r="N85">
+        <v>7.790593400000001</v>
+      </c>
+      <c r="O85">
+        <v>2.72670769</v>
+      </c>
+      <c r="P85">
+        <v>5.063885710000001</v>
+      </c>
+      <c r="Q85">
+        <v>5.553885710000001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.9312400757578481</v>
+      </c>
+      <c r="T85">
+        <v>4.029038907843093</v>
+      </c>
+      <c r="U85">
+        <v>0.0509</v>
+      </c>
+      <c r="V85">
+        <v>0.35</v>
+      </c>
+      <c r="W85">
+        <v>0.033085</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>4.857862700854795</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1849657959019829</v>
+      </c>
+      <c r="C86">
+        <v>30.18944582463768</v>
+      </c>
+      <c r="D86">
+        <v>69.41244582463767</v>
+      </c>
+      <c r="E86">
+        <v>11.55199999999999</v>
+      </c>
+      <c r="F86">
+        <v>40.15199999999999</v>
+      </c>
+      <c r="G86">
+        <v>0.929</v>
+      </c>
+      <c r="H86">
+        <v>19.2</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>10.3</v>
+      </c>
+      <c r="K86">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L86">
+        <v>9.81</v>
+      </c>
+      <c r="M86">
+        <v>2.0437368</v>
+      </c>
+      <c r="N86">
+        <v>7.766263200000001</v>
+      </c>
+      <c r="O86">
+        <v>2.71819212</v>
+      </c>
+      <c r="P86">
+        <v>5.048071080000001</v>
+      </c>
+      <c r="Q86">
+        <v>5.538071080000001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.9823399743873931</v>
+      </c>
+      <c r="T86">
+        <v>4.259736167365467</v>
+      </c>
+      <c r="U86">
+        <v>0.0509</v>
+      </c>
+      <c r="V86">
+        <v>0.35</v>
+      </c>
+      <c r="W86">
+        <v>0.033085</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>4.800031002035097</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1841602289251317</v>
+      </c>
+      <c r="C87">
+        <v>30.0961203298464</v>
+      </c>
+      <c r="D87">
+        <v>69.79712032984639</v>
+      </c>
+      <c r="E87">
+        <v>12.02999999999999</v>
+      </c>
+      <c r="F87">
+        <v>40.63</v>
+      </c>
+      <c r="G87">
+        <v>0.929</v>
+      </c>
+      <c r="H87">
+        <v>19.2</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>10.3</v>
+      </c>
+      <c r="K87">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L87">
+        <v>9.81</v>
+      </c>
+      <c r="M87">
+        <v>2.068067</v>
+      </c>
+      <c r="N87">
+        <v>7.741933000000001</v>
+      </c>
+      <c r="O87">
+        <v>2.70967655</v>
+      </c>
+      <c r="P87">
+        <v>5.032256450000001</v>
+      </c>
+      <c r="Q87">
+        <v>5.522256450000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>1.040253192834211</v>
+      </c>
+      <c r="T87">
+        <v>4.521193061490826</v>
+      </c>
+      <c r="U87">
+        <v>0.0509</v>
+      </c>
+      <c r="V87">
+        <v>0.35</v>
+      </c>
+      <c r="W87">
+        <v>0.033085</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>4.743560049069979</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1833546619482805</v>
+      </c>
+      <c r="C88">
+        <v>30.00708222467032</v>
+      </c>
+      <c r="D88">
+        <v>70.18608222467032</v>
+      </c>
+      <c r="E88">
+        <v>12.508</v>
+      </c>
+      <c r="F88">
+        <v>41.108</v>
+      </c>
+      <c r="G88">
+        <v>0.929</v>
+      </c>
+      <c r="H88">
+        <v>19.2</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>10.3</v>
+      </c>
+      <c r="K88">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L88">
+        <v>9.81</v>
+      </c>
+      <c r="M88">
+        <v>2.0923972</v>
+      </c>
+      <c r="N88">
+        <v>7.717602800000001</v>
+      </c>
+      <c r="O88">
+        <v>2.70116098</v>
+      </c>
+      <c r="P88">
+        <v>5.016441820000001</v>
+      </c>
+      <c r="Q88">
+        <v>5.506441820000001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>1.106439728202004</v>
+      </c>
+      <c r="T88">
+        <v>4.820000940491236</v>
+      </c>
+      <c r="U88">
+        <v>0.0509</v>
+      </c>
+      <c r="V88">
+        <v>0.35</v>
+      </c>
+      <c r="W88">
+        <v>0.033085</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>4.688402374080792</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1825490949714293</v>
+      </c>
+      <c r="C89">
+        <v>29.92240358843956</v>
+      </c>
+      <c r="D89">
+        <v>70.57940358843956</v>
+      </c>
+      <c r="E89">
+        <v>12.986</v>
+      </c>
+      <c r="F89">
+        <v>41.586</v>
+      </c>
+      <c r="G89">
+        <v>0.929</v>
+      </c>
+      <c r="H89">
+        <v>19.2</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>10.3</v>
+      </c>
+      <c r="K89">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L89">
+        <v>9.81</v>
+      </c>
+      <c r="M89">
+        <v>2.1167274</v>
+      </c>
+      <c r="N89">
+        <v>7.6932726</v>
+      </c>
+      <c r="O89">
+        <v>2.69264541</v>
+      </c>
+      <c r="P89">
+        <v>5.00062719</v>
+      </c>
+      <c r="Q89">
+        <v>5.490627190000001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>1.182808807472533</v>
+      </c>
+      <c r="T89">
+        <v>5.164779262414786</v>
+      </c>
+      <c r="U89">
+        <v>0.0509</v>
+      </c>
+      <c r="V89">
+        <v>0.35</v>
+      </c>
+      <c r="W89">
+        <v>0.033085</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>4.634512691620093</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1817435279945781</v>
+      </c>
+      <c r="C90">
+        <v>29.84215812531412</v>
+      </c>
+      <c r="D90">
+        <v>70.97715812531412</v>
+      </c>
+      <c r="E90">
+        <v>13.464</v>
+      </c>
+      <c r="F90">
+        <v>42.064</v>
+      </c>
+      <c r="G90">
+        <v>0.929</v>
+      </c>
+      <c r="H90">
+        <v>19.2</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>10.3</v>
+      </c>
+      <c r="K90">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L90">
+        <v>9.81</v>
+      </c>
+      <c r="M90">
+        <v>2.1410576</v>
+      </c>
+      <c r="N90">
+        <v>7.668942400000001</v>
+      </c>
+      <c r="O90">
+        <v>2.68412984</v>
+      </c>
+      <c r="P90">
+        <v>4.98481256</v>
+      </c>
+      <c r="Q90">
+        <v>5.47481256</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>1.271906066621485</v>
+      </c>
+      <c r="T90">
+        <v>5.567020637992263</v>
+      </c>
+      <c r="U90">
+        <v>0.0509</v>
+      </c>
+      <c r="V90">
+        <v>0.35</v>
+      </c>
+      <c r="W90">
+        <v>0.033085</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>4.581847774669864</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1809379610177269</v>
+      </c>
+      <c r="C91">
+        <v>29.76642121032748</v>
+      </c>
+      <c r="D91">
+        <v>71.37942121032748</v>
+      </c>
+      <c r="E91">
+        <v>13.942</v>
+      </c>
+      <c r="F91">
+        <v>42.542</v>
+      </c>
+      <c r="G91">
+        <v>0.929</v>
+      </c>
+      <c r="H91">
+        <v>19.2</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>10.3</v>
+      </c>
+      <c r="K91">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L91">
+        <v>9.81</v>
+      </c>
+      <c r="M91">
+        <v>2.1653878</v>
+      </c>
+      <c r="N91">
+        <v>7.644612200000001</v>
+      </c>
+      <c r="O91">
+        <v>2.67561427</v>
+      </c>
+      <c r="P91">
+        <v>4.96899793</v>
+      </c>
+      <c r="Q91">
+        <v>5.458997930000001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>1.377202827433881</v>
+      </c>
+      <c r="T91">
+        <v>6.042396809129279</v>
+      </c>
+      <c r="U91">
+        <v>0.0509</v>
+      </c>
+      <c r="V91">
+        <v>0.35</v>
+      </c>
+      <c r="W91">
+        <v>0.033085</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>4.530366338999417</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1816533940408757</v>
+      </c>
+      <c r="C92">
+        <v>28.93094146369644</v>
+      </c>
+      <c r="D92">
+        <v>71.02194146369644</v>
+      </c>
+      <c r="E92">
+        <v>14.41999999999999</v>
+      </c>
+      <c r="F92">
+        <v>43.02</v>
+      </c>
+      <c r="G92">
+        <v>0.929</v>
+      </c>
+      <c r="H92">
+        <v>19.2</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>10.3</v>
+      </c>
+      <c r="K92">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L92">
+        <v>9.81</v>
+      </c>
+      <c r="M92">
+        <v>2.30157</v>
+      </c>
+      <c r="N92">
+        <v>7.508430000000001</v>
+      </c>
+      <c r="O92">
+        <v>2.6279505</v>
+      </c>
+      <c r="P92">
+        <v>4.880479500000001</v>
+      </c>
+      <c r="Q92">
+        <v>5.370479500000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.503558940408758</v>
+      </c>
+      <c r="T92">
+        <v>6.6128482144937</v>
+      </c>
+      <c r="U92">
+        <v>0.0535</v>
+      </c>
+      <c r="V92">
+        <v>0.35</v>
+      </c>
+      <c r="W92">
+        <v>0.034775</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>4.262307902866304</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1808647270640246</v>
+      </c>
+      <c r="C93">
+        <v>28.84721709440264</v>
+      </c>
+      <c r="D93">
+        <v>71.41621709440264</v>
+      </c>
+      <c r="E93">
+        <v>14.898</v>
+      </c>
+      <c r="F93">
+        <v>43.498</v>
+      </c>
+      <c r="G93">
+        <v>0.929</v>
+      </c>
+      <c r="H93">
+        <v>19.2</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>10.3</v>
+      </c>
+      <c r="K93">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L93">
+        <v>9.81</v>
+      </c>
+      <c r="M93">
+        <v>2.327143</v>
+      </c>
+      <c r="N93">
+        <v>7.482857000000001</v>
+      </c>
+      <c r="O93">
+        <v>2.61899995</v>
+      </c>
+      <c r="P93">
+        <v>4.863857050000001</v>
+      </c>
+      <c r="Q93">
+        <v>5.353857050000001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.657994189600273</v>
+      </c>
+      <c r="T93">
+        <v>7.310066598827992</v>
+      </c>
+      <c r="U93">
+        <v>0.0535</v>
+      </c>
+      <c r="V93">
+        <v>0.35</v>
+      </c>
+      <c r="W93">
+        <v>0.034775</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>4.215469354483158</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1800760600871734</v>
+      </c>
+      <c r="C94">
+        <v>28.76789477552737</v>
+      </c>
+      <c r="D94">
+        <v>71.81489477552736</v>
+      </c>
+      <c r="E94">
+        <v>15.376</v>
+      </c>
+      <c r="F94">
+        <v>43.976</v>
+      </c>
+      <c r="G94">
+        <v>0.929</v>
+      </c>
+      <c r="H94">
+        <v>19.2</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>10.3</v>
+      </c>
+      <c r="K94">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L94">
+        <v>9.81</v>
+      </c>
+      <c r="M94">
+        <v>2.352716</v>
+      </c>
+      <c r="N94">
+        <v>7.457284</v>
+      </c>
+      <c r="O94">
+        <v>2.6100494</v>
+      </c>
+      <c r="P94">
+        <v>4.8472346</v>
+      </c>
+      <c r="Q94">
+        <v>5.3372346</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.851038251089668</v>
+      </c>
+      <c r="T94">
+        <v>8.181589579245859</v>
+      </c>
+      <c r="U94">
+        <v>0.0535</v>
+      </c>
+      <c r="V94">
+        <v>0.35</v>
+      </c>
+      <c r="W94">
+        <v>0.034775</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>4.169649035412689</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.1792873931103222</v>
+      </c>
+      <c r="C95">
+        <v>28.69304864365436</v>
+      </c>
+      <c r="D95">
+        <v>72.21804864365436</v>
+      </c>
+      <c r="E95">
+        <v>15.854</v>
+      </c>
+      <c r="F95">
+        <v>44.454</v>
+      </c>
+      <c r="G95">
+        <v>0.929</v>
+      </c>
+      <c r="H95">
+        <v>19.2</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>10.3</v>
+      </c>
+      <c r="K95">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L95">
+        <v>9.81</v>
+      </c>
+      <c r="M95">
+        <v>2.378289</v>
+      </c>
+      <c r="N95">
+        <v>7.431711</v>
+      </c>
+      <c r="O95">
+        <v>2.60109885</v>
+      </c>
+      <c r="P95">
+        <v>4.83061215</v>
+      </c>
+      <c r="Q95">
+        <v>5.320612150000001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>2.09923775871889</v>
+      </c>
+      <c r="T95">
+        <v>9.302119125497398</v>
+      </c>
+      <c r="U95">
+        <v>0.0535</v>
+      </c>
+      <c r="V95">
+        <v>0.35</v>
+      </c>
+      <c r="W95">
+        <v>0.034775</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>4.124814099548036</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.178498726133471</v>
+      </c>
+      <c r="C96">
+        <v>28.62275450951503</v>
+      </c>
+      <c r="D96">
+        <v>72.62575450951503</v>
+      </c>
+      <c r="E96">
+        <v>16.332</v>
+      </c>
+      <c r="F96">
+        <v>44.932</v>
+      </c>
+      <c r="G96">
+        <v>0.929</v>
+      </c>
+      <c r="H96">
+        <v>19.2</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>10.3</v>
+      </c>
+      <c r="K96">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L96">
+        <v>9.81</v>
+      </c>
+      <c r="M96">
+        <v>2.403862</v>
+      </c>
+      <c r="N96">
+        <v>7.406138</v>
+      </c>
+      <c r="O96">
+        <v>2.5921483</v>
+      </c>
+      <c r="P96">
+        <v>4.8139897</v>
+      </c>
+      <c r="Q96">
+        <v>5.303989700000001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>2.430170435557852</v>
+      </c>
+      <c r="T96">
+        <v>10.79615852049946</v>
+      </c>
+      <c r="U96">
+        <v>0.0535</v>
+      </c>
+      <c r="V96">
+        <v>0.35</v>
+      </c>
+      <c r="W96">
+        <v>0.034775</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>4.080933098489014</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.1777100591566198</v>
+      </c>
+      <c r="C97">
+        <v>28.55708990551378</v>
+      </c>
+      <c r="D97">
+        <v>73.03808990551379</v>
+      </c>
+      <c r="E97">
+        <v>16.81</v>
+      </c>
+      <c r="F97">
+        <v>45.41</v>
+      </c>
+      <c r="G97">
+        <v>0.929</v>
+      </c>
+      <c r="H97">
+        <v>19.2</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>10.3</v>
+      </c>
+      <c r="K97">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L97">
+        <v>9.81</v>
+      </c>
+      <c r="M97">
+        <v>2.429435</v>
+      </c>
+      <c r="N97">
+        <v>7.380565000000001</v>
+      </c>
+      <c r="O97">
+        <v>2.58319775</v>
+      </c>
+      <c r="P97">
+        <v>4.797367250000001</v>
+      </c>
+      <c r="Q97">
+        <v>5.287367250000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>2.8934761831324</v>
+      </c>
+      <c r="T97">
+        <v>12.88781367350234</v>
+      </c>
+      <c r="U97">
+        <v>0.0535</v>
+      </c>
+      <c r="V97">
+        <v>0.35</v>
+      </c>
+      <c r="W97">
+        <v>0.034775</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>4.037975907978604</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.1786061921797686</v>
+      </c>
+      <c r="C98">
+        <v>27.61092863674909</v>
+      </c>
+      <c r="D98">
+        <v>72.56992863674908</v>
+      </c>
+      <c r="E98">
+        <v>17.288</v>
+      </c>
+      <c r="F98">
+        <v>45.888</v>
+      </c>
+      <c r="G98">
+        <v>0.929</v>
+      </c>
+      <c r="H98">
+        <v>19.2</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>10.3</v>
+      </c>
+      <c r="K98">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L98">
+        <v>9.81</v>
+      </c>
+      <c r="M98">
+        <v>2.5789056</v>
+      </c>
+      <c r="N98">
+        <v>7.231094400000001</v>
+      </c>
+      <c r="O98">
+        <v>2.53088304</v>
+      </c>
+      <c r="P98">
+        <v>4.700211360000001</v>
+      </c>
+      <c r="Q98">
+        <v>5.190211360000001</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>3.588434804494212</v>
+      </c>
+      <c r="T98">
+        <v>16.02529640300661</v>
+      </c>
+      <c r="U98">
+        <v>0.0562</v>
+      </c>
+      <c r="V98">
+        <v>0.35</v>
+      </c>
+      <c r="W98">
+        <v>0.03653</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>3.803939159308507</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.1778350752029175</v>
+      </c>
+      <c r="C99">
+        <v>27.53541631044585</v>
+      </c>
+      <c r="D99">
+        <v>72.97241631044584</v>
+      </c>
+      <c r="E99">
+        <v>17.76599999999999</v>
+      </c>
+      <c r="F99">
+        <v>46.36599999999999</v>
+      </c>
+      <c r="G99">
+        <v>0.929</v>
+      </c>
+      <c r="H99">
+        <v>19.2</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>10.3</v>
+      </c>
+      <c r="K99">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L99">
+        <v>9.81</v>
+      </c>
+      <c r="M99">
+        <v>2.6057692</v>
+      </c>
+      <c r="N99">
+        <v>7.204230800000001</v>
+      </c>
+      <c r="O99">
+        <v>2.52148078</v>
+      </c>
+      <c r="P99">
+        <v>4.682750020000001</v>
+      </c>
+      <c r="Q99">
+        <v>5.172750020000001</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>4.746699173430578</v>
+      </c>
+      <c r="T99">
+        <v>21.2544342855138</v>
+      </c>
+      <c r="U99">
+        <v>0.0562</v>
+      </c>
+      <c r="V99">
+        <v>0.35</v>
+      </c>
+      <c r="W99">
+        <v>0.03653</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>3.76472329168677</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.1770639582260662</v>
+      </c>
+      <c r="C100">
+        <v>27.46439344158537</v>
+      </c>
+      <c r="D100">
+        <v>73.37939344158536</v>
+      </c>
+      <c r="E100">
+        <v>18.24399999999999</v>
+      </c>
+      <c r="F100">
+        <v>46.84399999999999</v>
+      </c>
+      <c r="G100">
+        <v>0.929</v>
+      </c>
+      <c r="H100">
+        <v>19.2</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>10.3</v>
+      </c>
+      <c r="K100">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L100">
+        <v>9.81</v>
+      </c>
+      <c r="M100">
+        <v>2.6326328</v>
+      </c>
+      <c r="N100">
+        <v>7.177367200000001</v>
+      </c>
+      <c r="O100">
+        <v>2.51207852</v>
+      </c>
+      <c r="P100">
+        <v>4.665288680000001</v>
+      </c>
+      <c r="Q100">
+        <v>5.155288680000001</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>7.063227911303305</v>
+      </c>
+      <c r="T100">
+        <v>31.71271005052815</v>
+      </c>
+      <c r="U100">
+        <v>0.0562</v>
+      </c>
+      <c r="V100">
+        <v>0.35</v>
+      </c>
+      <c r="W100">
+        <v>0.03653</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>3.726307747894048</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.1762928412492151</v>
+      </c>
+      <c r="C101">
+        <v>27.39793556639524</v>
+      </c>
+      <c r="D101">
+        <v>73.79093556639523</v>
+      </c>
+      <c r="E101">
+        <v>18.72199999999999</v>
+      </c>
+      <c r="F101">
+        <v>47.322</v>
+      </c>
+      <c r="G101">
+        <v>0.929</v>
+      </c>
+      <c r="H101">
+        <v>19.2</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>10.3</v>
+      </c>
+      <c r="K101">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="L101">
+        <v>9.81</v>
+      </c>
+      <c r="M101">
+        <v>2.6594964</v>
+      </c>
+      <c r="N101">
+        <v>7.1505036</v>
+      </c>
+      <c r="O101">
+        <v>2.50267626</v>
+      </c>
+      <c r="P101">
+        <v>4.647827340000001</v>
+      </c>
+      <c r="Q101">
+        <v>5.137827340000001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>14.01281412492149</v>
+      </c>
+      <c r="T101">
+        <v>63.08753734557123</v>
+      </c>
+      <c r="U101">
+        <v>0.0562</v>
+      </c>
+      <c r="V101">
+        <v>0.35</v>
+      </c>
+      <c r="W101">
+        <v>0.03653</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>3.688668275693098</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
